--- a/Proyecto Intermodular/Jira/Tablas Jira.xlsx
+++ b/Proyecto Intermodular/Jira/Tablas Jira.xlsx
@@ -6257,21 +6257,6 @@
     <t>- Al abrir “Crear quedada”, se muestran los campos obligatorios del formulario. - Los campos obligatorios muestran validación si se envían vacíos. - Los campos opcionales pueden omitirse sin impedir el envío. - Los campos con formato (ej. fecha/hora) validan el formato introducido. - Tras envío válido, se redirige al resumen de la quedada.</t>
   </si>
   <si>
-    <t>- El creador puede ver un formulario para asignar puntuación a cada equipo. - Se valida que la puntuación tenga un formato correcto (numérico). - No se permite dejar equipos sin puntuación si son obligatorios. - El formulario muestra todos los equipos de la quedada. - Si ocurre un error, se muestra mensaje y no se guarda.</t>
-  </si>
-  <si>
-    <t>- Se muestra la lista completa de equipos de la quedada. - Se muestran los usuarios participantes de cada equipo. - Los datos coinciden con lo almacenado en la base de datos. - Si no hay participantes, se indica visualmente. - Si ocurre error de carga, la página muestra aviso.</t>
-  </si>
-  <si>
-    <t>- Al enviar puntuaciones válidas, se guardan en la base de datos. - Se valida que las puntuaciones cumplan los requisitos numéricos. - Tras aplicar las puntuaciones, se muestra mensaje de confirmación. - Si ocurre un error, no se guardan los cambios. - Los usuarios participantes pueden ver las puntuaciones una vez aplicadas.</t>
-  </si>
-  <si>
-    <t>- Se muestra lista de quedadas que ya pasaron la fecha. - Se indica cuáles no cumplieron requisitos mínimos. - Las quedadas no válidas no se marcan como realizadas. - Si no hay ninguna, se muestra mensaje correspondiente. - Si hay error de carga, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- Los requisitos mínimos de la quedada se muestran claramente (ej. número mínimo de jugadores). - Si faltan datos, se muestra aviso. - El usuario puede expandir/colapsar la lista de requisitos. - Los requisitos coinciden con los definidos por el creador. - Si ocurre error, se muestra mensaje correspondiente.</t>
-  </si>
-  <si>
     <t>- El creador ve un botón “Traspasar dueño” junto a cada participante. - Al pulsarlo, se solicita confirmación. - Si se confirma, la propiedad de la quedada se transfiere al usuario seleccionado. - El nuevo dueño recibe notificación. - Si ocurre error, la transferencia no se realiza.</t>
   </si>
   <si>
@@ -6585,6 +6570,33 @@
  - Si no hay jugadores aún, se indica “Sin participantes”.
  - Si la información cambia, se actualiza al recargar.
  - Si ocurre un error de carga, se muestra mensaje de fallo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El creador puede ver un formulario para asignar puntuación a cada equipo.
+ - Se valida que la puntuación tenga un formato correcto (numérico).
+ - No se permite dejar equipos sin puntuación si son obligatorios.
+ - El formulario muestra todos los equipos de la quedada.
+ - Si ocurre un error, se muestra mensaje y no se guarda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestra la lista completa de equipos de la quedada.
+ - Se muestran los usuarios participantes de cada equipo.
+ - Los datos coinciden con lo almacenado en la base de datos.
+ - Si no hay participantes, se indica visualmente.
+ - Si ocurre error de carga, la página muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Al enviar las puntuaciones, se guardan en la base de datos.
+ - Se valida que las puntuaciones cumplan los requisitos numéricos.
+ - Tras aplicar las puntuaciones, se muestra mensaje de confirmación.
+ - Si ocurre un error, no se guardan los cambios.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se indica en los detalles de las quedadas que no cumplieron los requisitos mínimos.
+ - Las quedadas no válidas no se marcan como realizadas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Los requisitos mínimos de la quedada se muestran claramente (ej. número mínimo de jugadores).</t>
   </si>
 </sst>
 </file>
@@ -6854,7 +6866,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -6889,7 +6901,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -75985,7 +75997,7 @@
         <v>1868</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>1880</v>
@@ -76013,7 +76025,7 @@
         <v>1168</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>2027</v>
+        <v>2022</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>1882</v>
@@ -76027,7 +76039,7 @@
         <v>1171</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>2028</v>
+        <v>2023</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>1883</v>
@@ -76041,7 +76053,7 @@
         <v>1155</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>2029</v>
+        <v>2024</v>
       </c>
       <c r="E6" s="25" t="s">
         <v>1884</v>
@@ -76055,7 +76067,7 @@
         <v>1873</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>1885</v>
@@ -76069,7 +76081,7 @@
         <v>1671</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>2031</v>
+        <v>2026</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>1886</v>
@@ -76083,7 +76095,7 @@
         <v>1672</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>2032</v>
+        <v>2027</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>1887</v>
@@ -76097,7 +76109,7 @@
         <v>1670</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>2033</v>
+        <v>2028</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>1888</v>
@@ -76111,7 +76123,7 @@
         <v>1794</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>2034</v>
+        <v>2029</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>1889</v>
@@ -76125,7 +76137,7 @@
         <v>1650</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>1890</v>
@@ -76139,7 +76151,7 @@
         <v>1103</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>2036</v>
+        <v>2031</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>1891</v>
@@ -76153,7 +76165,7 @@
         <v>1874</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>2037</v>
+        <v>2032</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>1892</v>
@@ -76167,7 +76179,7 @@
         <v>1105</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>2038</v>
+        <v>2033</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>1893</v>
@@ -76181,7 +76193,7 @@
         <v>1669</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="E16" s="25" t="s">
         <v>1894</v>
@@ -76195,7 +76207,7 @@
         <v>1727</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>1895</v>
@@ -76209,7 +76221,7 @@
         <v>1151</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>1896</v>
@@ -76223,7 +76235,7 @@
         <v>1726</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>2042</v>
+        <v>2037</v>
       </c>
       <c r="E19" s="25" t="s">
         <v>1897</v>
@@ -76237,7 +76249,7 @@
         <v>1148</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>2043</v>
+        <v>2038</v>
       </c>
       <c r="E20" s="25" t="s">
         <v>1898</v>
@@ -76251,7 +76263,7 @@
         <v>1146</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>2044</v>
+        <v>2039</v>
       </c>
       <c r="E21" s="25" t="s">
         <v>1899</v>
@@ -76265,7 +76277,7 @@
         <v>1665</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="E22" s="25" t="s">
         <v>1900</v>
@@ -76279,7 +76291,7 @@
         <v>1660</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>2046</v>
+        <v>2041</v>
       </c>
       <c r="E23" s="25" t="s">
         <v>1901</v>
@@ -76293,7 +76305,7 @@
         <v>1132</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>2047</v>
+        <v>2042</v>
       </c>
       <c r="E24" s="25" t="s">
         <v>1902</v>
@@ -76307,7 +76319,7 @@
         <v>1659</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="E25" s="25" t="s">
         <v>1903</v>
@@ -76321,7 +76333,7 @@
         <v>1658</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>2049</v>
+        <v>2044</v>
       </c>
       <c r="E26" s="25" t="s">
         <v>1904</v>
@@ -76335,7 +76347,7 @@
         <v>1126</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="E27" s="25" t="s">
         <v>1905</v>
@@ -76349,7 +76361,7 @@
         <v>1657</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>2051</v>
+        <v>2046</v>
       </c>
       <c r="E28" s="25" t="s">
         <v>1906</v>
@@ -76363,7 +76375,7 @@
         <v>1228</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>2052</v>
+        <v>2047</v>
       </c>
       <c r="E29" s="25" t="s">
         <v>1907</v>
@@ -76377,7 +76389,7 @@
         <v>1872</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>2053</v>
+        <v>2048</v>
       </c>
       <c r="E30" s="25" t="s">
         <v>1908</v>
@@ -76391,7 +76403,7 @@
         <v>1663</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>2054</v>
+        <v>2049</v>
       </c>
       <c r="E31" s="25" t="s">
         <v>1909</v>
@@ -76405,80 +76417,80 @@
         <v>1229</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>2055</v>
+        <v>2050</v>
       </c>
       <c r="E32" s="25" t="s">
         <v>1910</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
         <v>1911</v>
       </c>
       <c r="B33" s="20" t="s">
         <v>1655</v>
       </c>
+      <c r="C33" s="24" t="s">
+        <v>2051</v>
+      </c>
       <c r="E33" s="25" t="s">
         <v>1911</v>
       </c>
-      <c r="F33" s="24" t="s">
-        <v>1969</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:6" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
         <v>1912</v>
       </c>
       <c r="B34" s="20" t="s">
         <v>1656</v>
       </c>
+      <c r="C34" s="24" t="s">
+        <v>2052</v>
+      </c>
       <c r="E34" s="25" t="s">
         <v>1912</v>
       </c>
-      <c r="F34" s="24" t="s">
-        <v>1970</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19" t="s">
         <v>1913</v>
       </c>
       <c r="B35" s="20" t="s">
         <v>1117</v>
       </c>
+      <c r="C35" s="24" t="s">
+        <v>2053</v>
+      </c>
       <c r="E35" s="25" t="s">
         <v>1913</v>
       </c>
-      <c r="F35" s="24" t="s">
-        <v>1971</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19" t="s">
         <v>1914</v>
       </c>
       <c r="B36" s="20" t="s">
         <v>1870</v>
       </c>
+      <c r="C36" s="24" t="s">
+        <v>2054</v>
+      </c>
       <c r="E36" s="25" t="s">
         <v>1914</v>
       </c>
-      <c r="F36" s="24" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19" t="s">
         <v>1915</v>
       </c>
       <c r="B37" s="20" t="s">
         <v>1871</v>
       </c>
+      <c r="C37" s="24" t="s">
+        <v>2055</v>
+      </c>
       <c r="E37" s="25" t="s">
         <v>1915</v>
-      </c>
-      <c r="F37" s="24" t="s">
-        <v>1973</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76492,7 +76504,7 @@
         <v>1916</v>
       </c>
       <c r="F38" s="24" t="s">
-        <v>1974</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76506,7 +76518,7 @@
         <v>1917</v>
       </c>
       <c r="F39" s="24" t="s">
-        <v>1975</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76520,7 +76532,7 @@
         <v>1918</v>
       </c>
       <c r="F40" s="24" t="s">
-        <v>1976</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76534,7 +76546,7 @@
         <v>1919</v>
       </c>
       <c r="F41" s="24" t="s">
-        <v>1977</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76548,7 +76560,7 @@
         <v>1920</v>
       </c>
       <c r="F42" s="24" t="s">
-        <v>1978</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76562,7 +76574,7 @@
         <v>1921</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>1979</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76576,7 +76588,7 @@
         <v>1922</v>
       </c>
       <c r="F44" s="24" t="s">
-        <v>1980</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76590,7 +76602,7 @@
         <v>1923</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>1981</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76604,7 +76616,7 @@
         <v>1924</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>1982</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76618,7 +76630,7 @@
         <v>1925</v>
       </c>
       <c r="F47" s="24" t="s">
-        <v>1983</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76632,7 +76644,7 @@
         <v>1926</v>
       </c>
       <c r="F48" s="24" t="s">
-        <v>1984</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76646,7 +76658,7 @@
         <v>1927</v>
       </c>
       <c r="F49" s="24" t="s">
-        <v>1985</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76660,7 +76672,7 @@
         <v>1928</v>
       </c>
       <c r="F50" s="24" t="s">
-        <v>1986</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76674,7 +76686,7 @@
         <v>1929</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>1987</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76688,7 +76700,7 @@
         <v>1930</v>
       </c>
       <c r="F52" s="24" t="s">
-        <v>1988</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76702,7 +76714,7 @@
         <v>1931</v>
       </c>
       <c r="F53" s="24" t="s">
-        <v>1989</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76716,7 +76728,7 @@
         <v>1932</v>
       </c>
       <c r="F54" s="24" t="s">
-        <v>1990</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76730,7 +76742,7 @@
         <v>1933</v>
       </c>
       <c r="F55" s="24" t="s">
-        <v>1991</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76744,7 +76756,7 @@
         <v>1934</v>
       </c>
       <c r="F56" s="24" t="s">
-        <v>1992</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76758,7 +76770,7 @@
         <v>1935</v>
       </c>
       <c r="F57" s="24" t="s">
-        <v>1993</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76772,7 +76784,7 @@
         <v>1936</v>
       </c>
       <c r="F58" s="24" t="s">
-        <v>1994</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76786,7 +76798,7 @@
         <v>1937</v>
       </c>
       <c r="F59" s="24" t="s">
-        <v>1995</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76800,7 +76812,7 @@
         <v>1938</v>
       </c>
       <c r="F60" s="24" t="s">
-        <v>1996</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76814,7 +76826,7 @@
         <v>1939</v>
       </c>
       <c r="F61" s="24" t="s">
-        <v>1997</v>
+        <v>1992</v>
       </c>
       <c r="G61" s="23"/>
       <c r="H61" s="23"/>
@@ -76830,7 +76842,7 @@
         <v>1940</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>1998</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76844,7 +76856,7 @@
         <v>1941</v>
       </c>
       <c r="F63" s="24" t="s">
-        <v>1999</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76858,7 +76870,7 @@
         <v>1942</v>
       </c>
       <c r="F64" s="24" t="s">
-        <v>2000</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76872,7 +76884,7 @@
         <v>1943</v>
       </c>
       <c r="F65" s="24" t="s">
-        <v>2001</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76886,7 +76898,7 @@
         <v>1944</v>
       </c>
       <c r="F66" s="24" t="s">
-        <v>2002</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76900,7 +76912,7 @@
         <v>1945</v>
       </c>
       <c r="F67" s="24" t="s">
-        <v>2003</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76914,7 +76926,7 @@
         <v>1946</v>
       </c>
       <c r="F68" s="24" t="s">
-        <v>2004</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76928,7 +76940,7 @@
         <v>1947</v>
       </c>
       <c r="F69" s="24" t="s">
-        <v>2005</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76942,7 +76954,7 @@
         <v>1948</v>
       </c>
       <c r="F70" s="24" t="s">
-        <v>2006</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76956,7 +76968,7 @@
         <v>1949</v>
       </c>
       <c r="F71" s="24" t="s">
-        <v>2007</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76970,7 +76982,7 @@
         <v>1950</v>
       </c>
       <c r="F72" s="24" t="s">
-        <v>2008</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76984,7 +76996,7 @@
         <v>1951</v>
       </c>
       <c r="F73" s="24" t="s">
-        <v>2009</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76998,7 +77010,7 @@
         <v>1952</v>
       </c>
       <c r="F74" s="24" t="s">
-        <v>2010</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -77012,7 +77024,7 @@
         <v>1953</v>
       </c>
       <c r="F75" s="24" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -77026,7 +77038,7 @@
         <v>1954</v>
       </c>
       <c r="F76" s="24" t="s">
-        <v>2012</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -77040,7 +77052,7 @@
         <v>1955</v>
       </c>
       <c r="F77" s="24" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -77054,7 +77066,7 @@
         <v>1956</v>
       </c>
       <c r="F78" s="24" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -77068,7 +77080,7 @@
         <v>1957</v>
       </c>
       <c r="F79" s="24" t="s">
-        <v>2015</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -77082,7 +77094,7 @@
         <v>1958</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>2016</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -77096,7 +77108,7 @@
         <v>1959</v>
       </c>
       <c r="F81" s="24" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G81" s="23"/>
       <c r="H81" s="23"/>
@@ -77112,7 +77124,7 @@
         <v>1960</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>2018</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -77126,7 +77138,7 @@
         <v>1961</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>2019</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -77140,7 +77152,7 @@
         <v>1962</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>2020</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -77154,7 +77166,7 @@
         <v>1963</v>
       </c>
       <c r="F85" s="24" t="s">
-        <v>2021</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -77168,7 +77180,7 @@
         <v>1964</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>2022</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -77182,7 +77194,7 @@
         <v>1965</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>2023</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -77196,7 +77208,7 @@
         <v>1966</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>2024</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -77210,7 +77222,7 @@
         <v>1967</v>
       </c>
       <c r="F89" s="24" t="s">
-        <v>2025</v>
+        <v>2020</v>
       </c>
     </row>
   </sheetData>

--- a/Proyecto Intermodular/Jira/Tablas Jira.xlsx
+++ b/Proyecto Intermodular/Jira/Tablas Jira.xlsx
@@ -6257,27 +6257,6 @@
     <t>- Al abrir “Crear quedada”, se muestran los campos obligatorios del formulario. - Los campos obligatorios muestran validación si se envían vacíos. - Los campos opcionales pueden omitirse sin impedir el envío. - Los campos con formato (ej. fecha/hora) validan el formato introducido. - Tras envío válido, se redirige al resumen de la quedada.</t>
   </si>
   <si>
-    <t>- El creador ve un botón “Traspasar dueño” junto a cada participante. - Al pulsarlo, se solicita confirmación. - Si se confirma, la propiedad de la quedada se transfiere al usuario seleccionado. - El nuevo dueño recibe notificación. - Si ocurre error, la transferencia no se realiza.</t>
-  </si>
-  <si>
-    <t>- El creador ve un botón “Quitar administrador” junto a administradores. - Si el usuario no es administrador, el botón no aparece. - Al confirmar, se retiran permisos de administrador. - El usuario afectado recibe notificación del cambio. - Si ocurre error, no se aplican cambios.</t>
-  </si>
-  <si>
-    <t>- El creador ve un botón “Hacer administrador” junto a los participantes elegibles. - Si ya es administrador, el botón no aparece. - Al confirmar, se asigna el rol de administrador. - El usuario recibe notificación del cambio. - Si ocurre un error, no se aplican los cambios.</t>
-  </si>
-  <si>
-    <t>- Se muestra una lista de todas las quedadas en las que el usuario es dueño o administrador. - Cada quedada muestra título, fecha, ubicación y estado. - Si no hay ninguna, se muestra mensaje correspondiente. - Si ocurre error de carga, aparece aviso. - Al pulsar una quedada, se accede a su panel de gestión.</t>
-  </si>
-  <si>
-    <t>- La pantalla de normas muestra todas las reglas creadas por el organizador. - Si no existen normas, se muestra un mensaje indicando que no hay reglas. - Las normas se muestran en orden definido por el creador. - El usuario puede desplazarse para ver normas largas. - Si hay error en la carga, se muestra mensaje de fallo.</t>
-  </si>
-  <si>
-    <t>- Las normas aparecen claramente identificadas dentro de la quedada. - El usuario puede acceder a ellas desde los detalles del evento. - Las normas son visibles para todos los participantes. - Si la quedada no tiene normas, se muestra mensaje informativo. - Si hay fallo al cargarlas, se muestra un aviso.</t>
-  </si>
-  <si>
-    <t>- En el panel de creación/edición aparece un campo para gestionar normas. - El creador puede añadir normas nuevas. - El creador puede editar normas existentes. - El creador puede borrar normas individuales. - Los cambios se guardan correctamente en la base de datos.</t>
-  </si>
-  <si>
     <t>- Las normas al crearse deben cumplir una longitud mínima. - Si el texto está vacío, se muestra un mensaje de validación. - No se permiten normas duplicadas. - Al guardar, las normas se validan antes de enviarse. - Si ocurre un error, se muestra aviso y no se guardan cambios.</t>
   </si>
   <si>
@@ -6327,90 +6306,6 @@
   </si>
   <si>
     <t>- La lista de favoritas muestra título, fecha y ubicación de cada quedada. - El usuario puede acceder a los detalles desde esta lista. - Si no hay favoritas, se muestra mensaje. - Si ocurre error al cargarlas, aparece aviso. - El usuario puede quitar quedadas de favoritos directamente desde la lista.</t>
-  </si>
-  <si>
-    <t>- La barra de búsqueda se muestra en la parte superior de la pantalla. - El usuario puede introducir texto libremente. - El sistema filtra usuarios conforme se escribe. - Si no hay resultados, se muestra un mensaje informativo. - Si ocurre error al buscar, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- El usuario puede activar uno o varios filtros disponibles. - Los filtros aplican cambios inmediatos en la lista. - Si no existe ningún usuario que coincida, se muestra mensaje. - El usuario puede reiniciar filtros para ver lista completa. - Si ocurre error al aplicar filtros, aparece aviso.</t>
-  </si>
-  <si>
-    <t>- Existe un botón de confirmación en el formulario de creación del grupo/chat. - Al confirmar, el sistema valida que toda la información esté completa. - Si falta información, se muestra mensaje indicando qué completar. - Al confirmar correctamente, se crea el grupo/chat. - Si ocurre error al crear, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- El formulario muestra campos para nombre, descripción e imagen del grupo/chat. - Los campos son editables desde cualquier dispositivo. - Si un campo obligatorio está incompleto, se marca visualmente. - Se puede previsualizar la imagen antes de crear. - Si falla la carga del formulario, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- En la sección del perfil aparece un botón de “Premium”. - El botón redirige a la página de información premium. - Si el usuario ya es premium, el botón cambia su estado o texto. - El botón es visible en todos los perfiles propios. - Si ocurre error al cargar, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- Se muestra una lista con todos los beneficios premium. - Se incluye información del precio, duración y requisitos. - Los beneficios están actualizados dinámicamente. - La información se presenta de forma clara y estructurada. - Si ocurre error de carga, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- La lista muestra todos los grupos y chats a los que pertenece el usuario. - Cada elemento de la lista permite acceder al chat. - Si no pertenece a ningún grupo/chat, se muestra mensaje. - La lista se actualiza automáticamente al unirse o salir. - Si ocurre error al cargar, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- El sistema muestra filtros disponibles para buscar grupos/chats. - El usuario puede activar uno o varios filtros. - La lista se actualiza al aplicar filtros. - Si no hay resultados, se muestra mensaje informativo. - Si los filtros fallan, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- La barra de búsqueda aparece en la sección de grupos/chats. - Se permite escribir cualquier texto. - La búsqueda aplica coincidencias parciales. - Si no hay resultados, se indica al usuario. - Si hay error, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- Existe un botón específico para confirmar la aplicación de filtros. - Al confirmar, la lista se actualiza con los resultados. - El usuario puede ver claramente qué filtros están activos. - Si no hay resultados, se indica en pantalla. - Si falla la operación, aparece mensaje.</t>
-  </si>
-  <si>
-    <t>- La pantalla de detalles del grupo muestra nombre, descripción e imagen. - Los datos se cargan correctamente desde la base de datos. - El usuario puede ver toda la información sin restricciones. - Si falta algún dato, se muestra de forma neutral. - Si ocurre error, se notifica.</t>
-  </si>
-  <si>
-    <t>- El formulario de edición muestra los datos actuales del grupo. - Todos los campos son editables por administradores/creador. - Los cambios deben pasar validaciones de texto e imagen. - Al guardar, se actualizan correctamente en la base de datos. - Si ocurre error, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- Junto a cada usuario del grupo se muestra un botón de “Traspasar dueño”. - Solo el creador puede ver y usar este botón. - Al pulsarlo, se solicita confirmación antes de aplicar cambios. - El nuevo dueño queda registrado correctamente. - Si ocurre error, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- La lista de participantes del grupo/chat se muestra ordenada. - Se incluyen nombre, foto y estado del usuario. - Si el grupo está vacío, se muestra mensaje. - Los participantes se actualizan en tiempo real si es posible. - Si hay error, se avisa al usuario.</t>
-  </si>
-  <si>
-    <t>- En la lista de participantes aparece un botón de “Quitar administrador”. - Solo el creador puede quitar administradores. - Se solicita confirmación antes de completar la acción. - Los cambios se guardan correctamente. - Si ocurre error, se notifica.</t>
-  </si>
-  <si>
-    <t>- En cada usuario del grupo aparece el botón “Eliminar usuario”. - Solo administradores/creador pueden usarlo. - Se solicita confirmación previa antes de eliminar. - El usuario eliminado desaparece de la lista inmediatamente. - Si ocurre error, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- El botón de “Hacer administrador” se muestra junto a cada usuario. - Solo el creador puede asignar administradores. - Al pulsarlo, se solicita confirmación. - El cambio se aplica correctamente en la base de datos. - Si ocurre error, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- En los detalles de la quedada se muestra un botón de “Modificar quedada”. - Solo el creador/administradores pueden verlo. - Al pulsarlo, redirige al formulario de edición. - El botón debe ser claramente identificable. - Si ocurre error al cargar, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- El formulario de modificación muestra los datos actuales de la quedada. - El usuario puede editar fecha, descripción, normas y otros campos permitidos. - Si un campo obligatorio queda vacío, se muestra advertencia. - Al guardar, los cambios se actualizan correctamente. - Si ocurre error, se muestra mensaje.</t>
-  </si>
-  <si>
-    <t>- Aparece un botón de “Denegar modificación” visible para participantes. - Al pulsarlo, el sistema solicita confirmación. - La acción bloquea temporalmente la modificación hasta consenso. - El estado de la votación se actualiza en tiempo real. - Si ocurre error, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- Aparece un botón de “Aceptar modificación” visible para los participantes. - Al pulsarlo, se solicita confirmación al usuario. - La aceptación se registra correctamente en la base de datos. - El estado de la votación se actualiza para todos los participantes. - Si ocurre error, se muestra un mensaje de aviso.</t>
-  </si>
-  <si>
-    <t>- Se muestra un cuadro de texto en la parte inferior del chat. - El usuario puede escribir mensajes sin límite mínimo. - Al enviar, el mensaje aparece inmediatamente en la conversación. - El cuadro de texto soporta salto de línea. - Si ocurre error al enviar, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- Se muestra un botón de imagen dentro del área de chat. - Permite seleccionar imágenes desde el dispositivo. - El sistema muestra una previsualización antes de enviar. - Al enviar, la imagen aparece integrada en la conversación. - Si ocurre error al cargar o enviar, se notifica al usuario.</t>
-  </si>
-  <si>
-    <t>- El formulario muestra campos para método de pago, datos y resumen. - Todos los campos obligatorios deben ser validados. - El usuario puede revisar el monto final antes de pagar. - La pasarela de pago procesa correctamente la transacción. - Si ocurre error de pago, el sistema avisa claramente.</t>
-  </si>
-  <si>
-    <t>- Se muestra un texto con los requisitos, costos y beneficios Premium. - El usuario debe marcar explícitamente que está de acuerdo. - Si intenta continuar sin aceptar, se muestra advertencia. - Al confirmar, se habilita el proceso de activación Premium. - Si ocurre error, aparece un mensaje informativo.</t>
-  </si>
-  <si>
-    <t>- Los usuarios no Premium ven anuncios integrados en las listas. - Los anuncios no bloquean la navegación. - Los anuncios se muestran en intervalos definidos. - Si el usuario es Premium, no se muestran. - Si ocurre error al cargar anuncios, el sistema lo indica.</t>
-  </si>
-  <si>
-    <t>- Tras completar el pago Premium, se envía un correo automático. - El correo contiene resumen de compra, costo, duración y beneficios. - El envío se registra correctamente en el sistema. - Si el correo no puede enviarse, se registra un error. - El usuario recibe el correo en un plazo razonable.</t>
-  </si>
-  <si>
-    <t>- En el perfil se muestra un indicador del tipo de cuenta. - Si el usuario es Premium, se muestra distintivo visible. - Si no lo es, aparece estado “No Premium”. - El estado se actualiza automáticamente tras el pago. - Si ocurre error al cargar el estado, se muestra aviso.</t>
   </si>
   <si>
     <t xml:space="preserve"> - El usuario autenticado visualiza su nombre, correo y foto al abrir el perfil.
@@ -6597,6 +6492,237 @@
   </si>
   <si>
     <t xml:space="preserve"> - Los requisitos mínimos de la quedada se muestran claramente (ej. número mínimo de jugadores).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El creador ve un botón “Traspasar dueño” junto a cada participante.
+ - Al pulsarlo, se solicita confirmación.
+ - Si se confirma, la propiedad de la quedada se transfiere al usuario seleccionado.
+ - Si ocurre error, la transferencia no se realiza.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El creador ve un botón “Quitar administrador” junto a administradores.
+ - Si el usuario no es administrador, el botón no aparece.
+ - Al confirmar, se retiran permisos de administrador.
+ - El usuario afectado recibe notificación del cambio.
+ - Si ocurre error, no se aplican cambios.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El creador ve un botón “Hacer administrador” junto a los participantes elegibles.
+ - Si ya es administrador, el botón no aparece.
+ - Al confirmar, se asigna el rol de administrador.
+ - El usuario recibe notificación del cambio.
+ - Si ocurre un error, no se aplican los cambios.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestra una lista de todas las quedadas en las que el usuario es dueño o administrador.
+ - Cada quedada muestra título, fecha, ubicación y estado.
+ - Si no hay ninguna, se muestra mensaje correspondiente.
+ - Si ocurre error de carga, aparece aviso.
+ - Al pulsar una quedada, se accede a su panel de gestión.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se visualiza una lista con todas las quedadas que aún no han finalidazo y que el usuario participa.
+ - Se muestra el botón de detalles de cada quedada para poder gestionar la quedada en la que participa el usuario.
+ - Si el usuario no tiene ninguna quedada pendiente aparece un mensaje de aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se visualiza una lista con todas las quedadas que ya han finalizado y que el suuario ha sido participante
+ - Se muestra el botón de detalles de cada quedada para poder ver la información de la quedada terminada.
+ - Si el usuario no tiene ninguna quedada finalizada aparece un mensaje de aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se visualiza el botón de eliminar participante en cada usuario que está en la quedada.
+ - Al pulsar el botón el usuario se elimina al usuario participante en la quedada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - En el perfil se muestra un indicador del tipo de cuenta.
+ - Si el usuario es Premium, se muestra distintivo visible.
+ - Si no lo es, aparece estado “No Premium”.
+ - El estado se actualiza automáticamente tras el pago.
+ - Si ocurre error al cargar el estado, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Tras completar el pago Premium, se envía un correo automático.
+ - El correo contiene resumen de compra, costo, duración y beneficios.
+ - El envío se registra correctamente en el sistema.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Los usuarios no Premium ven anuncios integrados en las listas.
+ - Los anuncios no bloquean la navegación.
+ - Los anuncios se muestran en intervalos definidos.
+ - Si el usuario es Premium, no se muestran.
+ - Si ocurre error al cargar anuncios, el sistema lo indica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestra un texto con los requisitos, costos y beneficios Premium.
+ - El usuario debe marcar explícitamente que está de acuerdo.
+ - Si intenta continuar sin aceptar, se muestra advertencia.
+ - Al confirmar, se habilita el proceso de activación Premium.
+ - Si ocurre error, aparece un mensaje informativo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El formulario muestra campos para método de pago, datos y resumen.
+ - Todos los campos obligatorios deben ser validados.
+ - El usuario puede revisar el monto final antes de pagar.
+ - La pasarela de pago procesa correctamente la transacción.
+ - Si ocurre error de pago, el sistema avisa claramente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestra un botón de imagen dentro del área de chat.
+ - Permite seleccionar imágenes desde el dispositivo.
+ - El sistema muestra una previsualización antes de enviar.
+ - Al enviar, la imagen aparece integrada en la conversación.
+ - Si ocurre error al cargar o enviar, se notifica al usuario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestra un cuadro de texto en la parte inferior del chat.
+ - El usuario puede escribir mensajes sin límite mínimo.
+ - Al enviar, el mensaje aparece inmediatamente en la conversación.
+ - Si ocurre error al enviar, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Aparece un botón de “Aceptar modificación” visible para los participantes.
+ - Al pulsarlo, se solicita confirmación al usuario.
+ - La aceptación se registra correctamente en la base de datos.
+ - El estado de la votación se actualiza para todos los participantes.
+ - Si ocurre error, se muestra un mensaje de aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Aparece un botón de “Denegar modificación” visible para participantes.
+ - Al pulsarlo, el sistema solicita confirmación.
+ - La acción bloquea la modificación hasta consenso.
+ - El estado de la votación se actualiza en tiempo real.
+ - Si ocurre error, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El formulario de modificación muestra los datos actuales de la quedada.
+ - El usuario puede editar fecha, descripción, y otros campos permitidos.
+ - Si un campo obligatorio queda vacío, se muestra advertencia.
+ - Si ocurre error, se muestra mensaje.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - En los detalles de la quedada se muestra un botón de “Modificar quedada”.
+ - Solo el creador/administradores pueden verlo.
+ - Al pulsarlo, redirige al formulario de edición.
+ - El botón debe ser claramente identificable.
+ - Si ocurre error al cargar, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El botón de “Hacer administrador” se muestra junto a cada usuario.
+ - Solo el creador puede asignar administradores.
+ - Al pulsarlo, se solicita confirmación.
+ - El cambio se aplica correctamente en la base de datos.
+ - Si ocurre error, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - En cada usuario del grupo aparece el botón “Eliminar usuario”.
+ - Solo administradores/creador pueden usarlo.
+ - Se solicita confirmación previa antes de eliminar.
+ - El usuario eliminado desaparece de la lista inmediatamente.
+ - Si ocurre error, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - En la lista de participantes aparece un botón de “Quitar administrador”.
+ - Solo el creador puede quitar administradores.
+ - Se solicita confirmación antes de completar la acción.
+ - Los cambios se guardan correctamente.
+ - Si ocurre error, se notifica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - La lista de participantes del grupo/chat se muestra ordenada.
+ - Se incluyen nombre y foto.
+ - Si el grupo está vacío, se muestra mensaje.
+ - Los participantes se actualizan en tiempo real.
+ - Si hay error, se avisa al usuario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Junto a cada usuario del grupo se muestra un botón de “Traspasar dueño”.
+ - Solo el creador puede ver y usar este botón.
+ - Al pulsarlo, se solicita confirmación antes de aplicar cambios.
+ - El nuevo dueño queda registrado correctamente.
+ - Si ocurre error, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El formulario de edición muestra los datos actuales del grupo.
+ - Todos los campos son editables por administradores/creador.
+ - Los cambios deben pasar validaciones.
+ - Al guardar, se actualizan correctamente en la base de datos.
+ - Si ocurre error, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - La pantalla de detalles del grupo muestra nombre, descripción e imagen.
+ - Los datos se cargan correctamente desde la base de datos.
+ - El usuario puede ver toda la información.
+ - Si falta algún dato, se muestra de forma neutral.
+ - Si ocurre error, se notifica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Existe un botón específico para confirmar la aplicación de filtros.
+ - Al confirmar, la lista se actualiza con los resultados.
+ - Si no hay resultados, se indica en pantalla.
+ - Si falla la operación, aparece mensaje.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - La barra de búsqueda aparece en la sección de grupos/chats.
+ - Se permite escribir cualquier texto.
+ - La búsqueda aplica coincidencias parciales.
+ - Si no hay resultados, se indica al usuario.
+ - Si hay error, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El sistema muestra filtros disponibles para buscar grupos/chats.
+ - El usuario puede activar uno o varios filtros.
+ - La lista se actualiza al aplicar filtros.
+ - Si no hay resultados, se muestra mensaje informativo.
+ - Si los filtros fallan, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - La lista muestra todos los grupos y chats a los que pertenece el usuario.
+ - Cada elemento de la lista permite acceder al chat.
+ - Si no pertenece a ningún grupo/chat, se muestra mensaje.
+ - La lista se actualiza automáticamente al unirse o salir.
+ - Si ocurre error al cargar, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestra una lista con todos los beneficios premium.
+ - Se incluye información del precio, duración y requisitos.
+ - Los beneficios están actualizados dinámicamente.
+ - La información se presenta de forma clara y estructurada.
+ - Si ocurre error de carga, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - En la sección del perfil aparece un botón de “Premium”.
+ - El botón redirige a la página de información premium.
+ - Si el usuario ya es premium, el botón cambia su estado o texto.
+ - El botón es visible en todos los perfiles propios.
+ - Si ocurre error al cargar, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El formulario muestra campos para nombre, descripción e imagen del grupo/chat. 
+ - Si un campo obligatorio está incompleto, se marca visualmente.
+ - Se puede previsualizar la imagen antes de crear.
+ - Si falla la carga del formulario, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Existe un botón de confirmación en el formulario de creación del grupo/chat.
+ - Al confirmar, el sistema valida que toda la información esté completa.
+ - Si falta información, se muestra mensaje indicando qué completar.
+ - Al confirmar correctamente, se crea el grupo/chat.
+ - Si ocurre error al crear, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El usuario puede activar uno o varios filtros disponibles.
+ - Los filtros aplican cambios inmediatos en la lista.
+ - Si no existe ningún usuario que coincida, se muestra mensaje.
+ - El usuario puede reiniciar filtros para ver lista completa.
+ - Si ocurre error al aplicar filtros, aparece aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - La barra de búsqueda se muestra en la parte superior de la pantalla.
+ - El usuario puede introducir texto libremente.
+ - El sistema filtra usuarios conforme se escribe.
+ - Si no hay resultados, se muestra un mensaje informativo.
+ - Si ocurre error al buscar, se muestra aviso.</t>
   </si>
 </sst>
 </file>
@@ -75997,7 +76123,7 @@
         <v>1868</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>2021</v>
+        <v>1986</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>1880</v>
@@ -76025,7 +76151,7 @@
         <v>1168</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>2022</v>
+        <v>1987</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>1882</v>
@@ -76039,7 +76165,7 @@
         <v>1171</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>2023</v>
+        <v>1988</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>1883</v>
@@ -76053,7 +76179,7 @@
         <v>1155</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>2024</v>
+        <v>1989</v>
       </c>
       <c r="E6" s="25" t="s">
         <v>1884</v>
@@ -76067,7 +76193,7 @@
         <v>1873</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>2025</v>
+        <v>1990</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>1885</v>
@@ -76081,7 +76207,7 @@
         <v>1671</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>2026</v>
+        <v>1991</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>1886</v>
@@ -76095,7 +76221,7 @@
         <v>1672</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>2027</v>
+        <v>1992</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>1887</v>
@@ -76109,7 +76235,7 @@
         <v>1670</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>2028</v>
+        <v>1993</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>1888</v>
@@ -76123,7 +76249,7 @@
         <v>1794</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>2029</v>
+        <v>1994</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>1889</v>
@@ -76137,7 +76263,7 @@
         <v>1650</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>2030</v>
+        <v>1995</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>1890</v>
@@ -76151,7 +76277,7 @@
         <v>1103</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>2031</v>
+        <v>1996</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>1891</v>
@@ -76165,7 +76291,7 @@
         <v>1874</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>2032</v>
+        <v>1997</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>1892</v>
@@ -76179,7 +76305,7 @@
         <v>1105</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>2033</v>
+        <v>1998</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>1893</v>
@@ -76193,7 +76319,7 @@
         <v>1669</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>2034</v>
+        <v>1999</v>
       </c>
       <c r="E16" s="25" t="s">
         <v>1894</v>
@@ -76207,7 +76333,7 @@
         <v>1727</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>2035</v>
+        <v>2000</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>1895</v>
@@ -76221,7 +76347,7 @@
         <v>1151</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>2036</v>
+        <v>2001</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>1896</v>
@@ -76235,7 +76361,7 @@
         <v>1726</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>2037</v>
+        <v>2002</v>
       </c>
       <c r="E19" s="25" t="s">
         <v>1897</v>
@@ -76249,7 +76375,7 @@
         <v>1148</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>2038</v>
+        <v>2003</v>
       </c>
       <c r="E20" s="25" t="s">
         <v>1898</v>
@@ -76263,7 +76389,7 @@
         <v>1146</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>2039</v>
+        <v>2004</v>
       </c>
       <c r="E21" s="25" t="s">
         <v>1899</v>
@@ -76277,7 +76403,7 @@
         <v>1665</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>2040</v>
+        <v>2005</v>
       </c>
       <c r="E22" s="25" t="s">
         <v>1900</v>
@@ -76291,7 +76417,7 @@
         <v>1660</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>2041</v>
+        <v>2006</v>
       </c>
       <c r="E23" s="25" t="s">
         <v>1901</v>
@@ -76305,7 +76431,7 @@
         <v>1132</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>2042</v>
+        <v>2007</v>
       </c>
       <c r="E24" s="25" t="s">
         <v>1902</v>
@@ -76319,7 +76445,7 @@
         <v>1659</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>2043</v>
+        <v>2008</v>
       </c>
       <c r="E25" s="25" t="s">
         <v>1903</v>
@@ -76333,7 +76459,7 @@
         <v>1658</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>2044</v>
+        <v>2009</v>
       </c>
       <c r="E26" s="25" t="s">
         <v>1904</v>
@@ -76347,7 +76473,7 @@
         <v>1126</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>2045</v>
+        <v>2010</v>
       </c>
       <c r="E27" s="25" t="s">
         <v>1905</v>
@@ -76361,7 +76487,7 @@
         <v>1657</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>2046</v>
+        <v>2011</v>
       </c>
       <c r="E28" s="25" t="s">
         <v>1906</v>
@@ -76375,7 +76501,7 @@
         <v>1228</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>2047</v>
+        <v>2012</v>
       </c>
       <c r="E29" s="25" t="s">
         <v>1907</v>
@@ -76389,7 +76515,7 @@
         <v>1872</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>2048</v>
+        <v>2013</v>
       </c>
       <c r="E30" s="25" t="s">
         <v>1908</v>
@@ -76403,7 +76529,7 @@
         <v>1663</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>2049</v>
+        <v>2014</v>
       </c>
       <c r="E31" s="25" t="s">
         <v>1909</v>
@@ -76417,7 +76543,7 @@
         <v>1229</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>2050</v>
+        <v>2015</v>
       </c>
       <c r="E32" s="25" t="s">
         <v>1910</v>
@@ -76431,7 +76557,7 @@
         <v>1655</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>2051</v>
+        <v>2016</v>
       </c>
       <c r="E33" s="25" t="s">
         <v>1911</v>
@@ -76445,7 +76571,7 @@
         <v>1656</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>2052</v>
+        <v>2017</v>
       </c>
       <c r="E34" s="25" t="s">
         <v>1912</v>
@@ -76459,7 +76585,7 @@
         <v>1117</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>2053</v>
+        <v>2018</v>
       </c>
       <c r="E35" s="25" t="s">
         <v>1913</v>
@@ -76473,7 +76599,7 @@
         <v>1870</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>2054</v>
+        <v>2019</v>
       </c>
       <c r="E36" s="25" t="s">
         <v>1914</v>
@@ -76487,94 +76613,94 @@
         <v>1871</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>2055</v>
+        <v>2020</v>
       </c>
       <c r="E37" s="25" t="s">
         <v>1915</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="19" t="s">
         <v>1916</v>
       </c>
       <c r="B38" s="20" t="s">
         <v>1792</v>
       </c>
+      <c r="C38" s="24" t="s">
+        <v>2021</v>
+      </c>
       <c r="E38" s="25" t="s">
         <v>1916</v>
       </c>
-      <c r="F38" s="24" t="s">
-        <v>1969</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19" t="s">
         <v>1917</v>
       </c>
       <c r="B39" s="20" t="s">
         <v>1637</v>
       </c>
+      <c r="C39" s="24" t="s">
+        <v>2022</v>
+      </c>
       <c r="E39" s="25" t="s">
         <v>1917</v>
       </c>
-      <c r="F39" s="24" t="s">
-        <v>1970</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19" t="s">
         <v>1918</v>
       </c>
       <c r="B40" s="20" t="s">
         <v>1661</v>
       </c>
+      <c r="C40" s="24" t="s">
+        <v>2023</v>
+      </c>
       <c r="E40" s="25" t="s">
         <v>1918</v>
       </c>
-      <c r="F40" s="24" t="s">
-        <v>1971</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:6" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
         <v>1919</v>
       </c>
       <c r="B41" s="20" t="s">
         <v>1795</v>
       </c>
+      <c r="C41" s="24" t="s">
+        <v>2024</v>
+      </c>
       <c r="E41" s="25" t="s">
         <v>1919</v>
       </c>
-      <c r="F41" s="24" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="19" t="s">
         <v>1920</v>
       </c>
       <c r="B42" s="20" t="s">
         <v>1244</v>
       </c>
+      <c r="C42" s="24" t="s">
+        <v>2025</v>
+      </c>
       <c r="E42" s="25" t="s">
         <v>1920</v>
       </c>
-      <c r="F42" s="24" t="s">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="19" t="s">
         <v>1921</v>
       </c>
       <c r="B43" s="20" t="s">
         <v>1869</v>
       </c>
+      <c r="C43" s="24" t="s">
+        <v>2026</v>
+      </c>
       <c r="E43" s="25" t="s">
         <v>1921</v>
-      </c>
-      <c r="F43" s="24" t="s">
-        <v>1974</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76584,11 +76710,11 @@
       <c r="B44" s="20" t="s">
         <v>1662</v>
       </c>
+      <c r="C44" s="24" t="s">
+        <v>2027</v>
+      </c>
       <c r="E44" s="25" t="s">
         <v>1922</v>
-      </c>
-      <c r="F44" s="24" t="s">
-        <v>1975</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76602,7 +76728,7 @@
         <v>1923</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>1976</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76616,7 +76742,7 @@
         <v>1924</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>1977</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76630,7 +76756,7 @@
         <v>1925</v>
       </c>
       <c r="F47" s="24" t="s">
-        <v>1978</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76644,7 +76770,7 @@
         <v>1926</v>
       </c>
       <c r="F48" s="24" t="s">
-        <v>1979</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76658,7 +76784,7 @@
         <v>1927</v>
       </c>
       <c r="F49" s="24" t="s">
-        <v>1980</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76672,7 +76798,7 @@
         <v>1928</v>
       </c>
       <c r="F50" s="24" t="s">
-        <v>1981</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76686,7 +76812,7 @@
         <v>1929</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>1982</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76700,7 +76826,7 @@
         <v>1930</v>
       </c>
       <c r="F52" s="24" t="s">
-        <v>1983</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76714,7 +76840,7 @@
         <v>1931</v>
       </c>
       <c r="F53" s="24" t="s">
-        <v>1984</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76728,7 +76854,7 @@
         <v>1932</v>
       </c>
       <c r="F54" s="24" t="s">
-        <v>1985</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76742,7 +76868,7 @@
         <v>1933</v>
       </c>
       <c r="F55" s="24" t="s">
-        <v>1986</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76756,7 +76882,7 @@
         <v>1934</v>
       </c>
       <c r="F56" s="24" t="s">
-        <v>1987</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76770,7 +76896,7 @@
         <v>1935</v>
       </c>
       <c r="F57" s="24" t="s">
-        <v>1988</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76784,7 +76910,7 @@
         <v>1936</v>
       </c>
       <c r="F58" s="24" t="s">
-        <v>1989</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76798,7 +76924,7 @@
         <v>1937</v>
       </c>
       <c r="F59" s="24" t="s">
-        <v>1990</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76812,7 +76938,7 @@
         <v>1938</v>
       </c>
       <c r="F60" s="24" t="s">
-        <v>1991</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -76826,375 +76952,375 @@
         <v>1939</v>
       </c>
       <c r="F61" s="24" t="s">
-        <v>1992</v>
+        <v>1985</v>
       </c>
       <c r="G61" s="23"/>
       <c r="H61" s="23"/>
     </row>
-    <row r="62" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="19" t="s">
         <v>1940</v>
       </c>
       <c r="B62" s="20" t="s">
         <v>1210</v>
       </c>
+      <c r="C62" s="24" t="s">
+        <v>2055</v>
+      </c>
       <c r="E62" s="25" t="s">
         <v>1940</v>
       </c>
-      <c r="F62" s="24" t="s">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:8" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="19" t="s">
         <v>1941</v>
       </c>
       <c r="B63" s="20" t="s">
         <v>1208</v>
       </c>
+      <c r="C63" s="24" t="s">
+        <v>2054</v>
+      </c>
       <c r="E63" s="25" t="s">
         <v>1941</v>
       </c>
-      <c r="F63" s="24" t="s">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:8" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="19" t="s">
         <v>1942</v>
       </c>
       <c r="B64" s="20" t="s">
         <v>1642</v>
       </c>
+      <c r="C64" s="24" t="s">
+        <v>2053</v>
+      </c>
       <c r="E64" s="25" t="s">
         <v>1942</v>
       </c>
-      <c r="F64" s="24" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="19" t="s">
         <v>1943</v>
       </c>
       <c r="B65" s="20" t="s">
         <v>1643</v>
       </c>
+      <c r="C65" s="24" t="s">
+        <v>2052</v>
+      </c>
       <c r="E65" s="25" t="s">
         <v>1943</v>
       </c>
-      <c r="F65" s="24" t="s">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:5" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="19" t="s">
         <v>1944</v>
       </c>
       <c r="B66" s="20" t="s">
         <v>1646</v>
       </c>
+      <c r="C66" s="24" t="s">
+        <v>2051</v>
+      </c>
       <c r="E66" s="25" t="s">
         <v>1944</v>
       </c>
-      <c r="F66" s="24" t="s">
-        <v>1997</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:5" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="19" t="s">
         <v>1945</v>
       </c>
       <c r="B67" s="20" t="s">
         <v>1080</v>
       </c>
+      <c r="C67" s="24" t="s">
+        <v>2050</v>
+      </c>
       <c r="E67" s="25" t="s">
         <v>1945</v>
       </c>
-      <c r="F67" s="24" t="s">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="19" t="s">
         <v>1946</v>
       </c>
       <c r="B68" s="20" t="s">
         <v>1073</v>
       </c>
+      <c r="C68" s="24" t="s">
+        <v>2049</v>
+      </c>
       <c r="E68" s="25" t="s">
         <v>1946</v>
       </c>
-      <c r="F68" s="24" t="s">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="19" t="s">
         <v>1947</v>
       </c>
       <c r="B69" s="20" t="s">
         <v>1866</v>
       </c>
+      <c r="C69" s="24" t="s">
+        <v>2048</v>
+      </c>
       <c r="E69" s="25" t="s">
         <v>1947</v>
       </c>
-      <c r="F69" s="24" t="s">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="19" t="s">
         <v>1948</v>
       </c>
       <c r="B70" s="20" t="s">
         <v>1724</v>
       </c>
+      <c r="C70" s="24" t="s">
+        <v>2047</v>
+      </c>
       <c r="E70" s="25" t="s">
         <v>1948</v>
       </c>
-      <c r="F70" s="24" t="s">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="19" t="s">
         <v>1949</v>
       </c>
       <c r="B71" s="20" t="s">
         <v>1723</v>
       </c>
+      <c r="C71" s="24" t="s">
+        <v>2046</v>
+      </c>
       <c r="E71" s="25" t="s">
         <v>1949</v>
       </c>
-      <c r="F71" s="24" t="s">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="19" t="s">
         <v>1950</v>
       </c>
       <c r="B72" s="20" t="s">
         <v>1635</v>
       </c>
+      <c r="C72" s="24" t="s">
+        <v>2045</v>
+      </c>
       <c r="E72" s="25" t="s">
         <v>1950</v>
       </c>
-      <c r="F72" s="24" t="s">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:5" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="19" t="s">
         <v>1951</v>
       </c>
       <c r="B73" s="20" t="s">
         <v>1633</v>
       </c>
+      <c r="C73" s="24" t="s">
+        <v>2044</v>
+      </c>
       <c r="E73" s="25" t="s">
         <v>1951</v>
       </c>
-      <c r="F73" s="24" t="s">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="19" t="s">
         <v>1952</v>
       </c>
       <c r="B74" s="20" t="s">
         <v>1793</v>
       </c>
+      <c r="C74" s="24" t="s">
+        <v>2043</v>
+      </c>
       <c r="E74" s="25" t="s">
         <v>1952</v>
       </c>
-      <c r="F74" s="24" t="s">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="19" t="s">
         <v>1953</v>
       </c>
       <c r="B75" s="20" t="s">
         <v>1058</v>
       </c>
+      <c r="C75" s="24" t="s">
+        <v>2042</v>
+      </c>
       <c r="E75" s="25" t="s">
         <v>1953</v>
       </c>
-      <c r="F75" s="24" t="s">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="19" t="s">
         <v>1954</v>
       </c>
       <c r="B76" s="20" t="s">
         <v>1639</v>
       </c>
+      <c r="C76" s="24" t="s">
+        <v>2041</v>
+      </c>
       <c r="E76" s="25" t="s">
         <v>1954</v>
       </c>
-      <c r="F76" s="24" t="s">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="19" t="s">
         <v>1955</v>
       </c>
       <c r="B77" s="20" t="s">
         <v>1640</v>
       </c>
+      <c r="C77" s="24" t="s">
+        <v>2040</v>
+      </c>
       <c r="E77" s="25" t="s">
         <v>1955</v>
       </c>
-      <c r="F77" s="24" t="s">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="19" t="s">
         <v>1956</v>
       </c>
       <c r="B78" s="20" t="s">
         <v>1641</v>
       </c>
+      <c r="C78" s="24" t="s">
+        <v>2039</v>
+      </c>
       <c r="E78" s="25" t="s">
         <v>1956</v>
       </c>
-      <c r="F78" s="24" t="s">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="19" t="s">
         <v>1957</v>
       </c>
       <c r="B79" s="20" t="s">
         <v>1207</v>
       </c>
+      <c r="C79" s="24" t="s">
+        <v>2038</v>
+      </c>
       <c r="E79" s="25" t="s">
         <v>1957</v>
       </c>
-      <c r="F79" s="24" t="s">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="19" t="s">
         <v>1958</v>
       </c>
       <c r="B80" s="20" t="s">
         <v>1204</v>
       </c>
+      <c r="C80" s="24" t="s">
+        <v>2037</v>
+      </c>
       <c r="E80" s="25" t="s">
         <v>1958</v>
       </c>
-      <c r="F80" s="24" t="s">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="19" t="s">
         <v>1959</v>
       </c>
       <c r="B81" s="20" t="s">
         <v>1205</v>
       </c>
+      <c r="C81" s="24" t="s">
+        <v>2036</v>
+      </c>
       <c r="E81" s="25" t="s">
         <v>1959</v>
       </c>
-      <c r="F81" s="24" t="s">
-        <v>2012</v>
-      </c>
       <c r="G81" s="23"/>
       <c r="H81" s="23"/>
     </row>
-    <row r="82" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="19" t="s">
         <v>1960</v>
       </c>
       <c r="B82" s="20" t="s">
         <v>1206</v>
       </c>
+      <c r="C82" s="24" t="s">
+        <v>2035</v>
+      </c>
       <c r="E82" s="25" t="s">
         <v>1960</v>
       </c>
-      <c r="F82" s="24" t="s">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="19" t="s">
         <v>1961</v>
       </c>
       <c r="B83" s="20" t="s">
         <v>1632</v>
       </c>
+      <c r="C83" s="24" t="s">
+        <v>2034</v>
+      </c>
       <c r="E83" s="25" t="s">
         <v>1961</v>
       </c>
-      <c r="F83" s="24" t="s">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:8" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="19" t="s">
         <v>1962</v>
       </c>
       <c r="B84" s="20" t="s">
         <v>1865</v>
       </c>
+      <c r="C84" s="24" t="s">
+        <v>2033</v>
+      </c>
       <c r="E84" s="25" t="s">
         <v>1962</v>
       </c>
-      <c r="F84" s="24" t="s">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:8" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="19" t="s">
         <v>1963</v>
       </c>
       <c r="B85" s="20" t="s">
         <v>1645</v>
       </c>
+      <c r="C85" s="24" t="s">
+        <v>2032</v>
+      </c>
       <c r="E85" s="25" t="s">
         <v>1963</v>
       </c>
-      <c r="F85" s="24" t="s">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:8" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="19" t="s">
         <v>1964</v>
       </c>
       <c r="B86" s="20" t="s">
         <v>1077</v>
       </c>
+      <c r="C86" s="24" t="s">
+        <v>2031</v>
+      </c>
       <c r="E86" s="25" t="s">
         <v>1964</v>
       </c>
-      <c r="F86" s="24" t="s">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="19" t="s">
         <v>1965</v>
       </c>
       <c r="B87" s="20" t="s">
         <v>1867</v>
       </c>
+      <c r="C87" s="24" t="s">
+        <v>2030</v>
+      </c>
       <c r="E87" s="25" t="s">
         <v>1965</v>
-      </c>
-      <c r="F87" s="24" t="s">
-        <v>2018</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -77204,25 +77330,25 @@
       <c r="B88" s="20" t="s">
         <v>1644</v>
       </c>
+      <c r="C88" s="24" t="s">
+        <v>2029</v>
+      </c>
       <c r="E88" s="25" t="s">
         <v>1966</v>
       </c>
-      <c r="F88" s="24" t="s">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:8" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="19" t="s">
         <v>1967</v>
       </c>
       <c r="B89" s="20" t="s">
         <v>1064</v>
       </c>
+      <c r="C89" s="24" t="s">
+        <v>2028</v>
+      </c>
       <c r="E89" s="25" t="s">
         <v>1967</v>
-      </c>
-      <c r="F89" s="24" t="s">
-        <v>2020</v>
       </c>
     </row>
   </sheetData>

--- a/Proyecto Intermodular/Jira/Tablas Jira.xlsx
+++ b/Proyecto Intermodular/Jira/Tablas Jira.xlsx
@@ -348,7 +348,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20828" uniqueCount="2056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20738" uniqueCount="2056">
   <si>
     <t>Resumen</t>
   </si>
@@ -6255,57 +6255,6 @@
   </si>
   <si>
     <t>- Al abrir “Crear quedada”, se muestran los campos obligatorios del formulario. - Los campos obligatorios muestran validación si se envían vacíos. - Los campos opcionales pueden omitirse sin impedir el envío. - Los campos con formato (ej. fecha/hora) validan el formato introducido. - Tras envío válido, se redirige al resumen de la quedada.</t>
-  </si>
-  <si>
-    <t>- Las normas al crearse deben cumplir una longitud mínima. - Si el texto está vacío, se muestra un mensaje de validación. - No se permiten normas duplicadas. - Al guardar, las normas se validan antes de enviarse. - Si ocurre un error, se muestra aviso y no se guardan cambios.</t>
-  </si>
-  <si>
-    <t>- El sistema notifica al creador cuando faltan datos por definir. - Los campos incompletos aparecen resaltados. - El creador recibe un resumen de qué falta rellenar. - No se permite publicar la quedada si faltan datos obligatorios. - Si la validación falla por error del sistema, aparece un mensaje.</t>
-  </si>
-  <si>
-    <t>- Antes de publicar, el creador puede revisar una vista previa completa. - La vista previa incluye ubicación, fecha, equipos, normas y descripción. - El creador puede volver atrás para editar cualquier sección. - La vista previa coincide con lo que verán los demás usuarios. - Si no se puede generar, el sistema muestra error.</t>
-  </si>
-  <si>
-    <t>- El creador puede definir requisitos mínimos para dar la quedada por válida. - Los requisitos disponibles se muestran en una lista editable. - Se puede activar/desactivar cada requisito. - Los requisitos quedan guardados correctamente. - Si hay error al guardar, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- Los requisitos definidos por el creador se muestran dentro del panel de validación. - Los administradores pueden consultarlos en cualquier momento. - Los requisitos se cargan correctamente desde la base de datos. - Si no hay requisitos definidos, se muestra mensaje. - Si ocurre un error, se informa al usuario.</t>
-  </si>
-  <si>
-    <t>- Tras finalizar la quedada, el sistema evalúa si cumple los requisitos definidos. - Cada requisito se marca como “cumplido” o “no cumplido”. - Se muestra un resultado global de validación. - Si falta información para validar, el sistema lo indica. - Si ocurre error, se muestra un aviso.</t>
-  </si>
-  <si>
-    <t>- La quedada queda marcada como “válida” solo si se cumplen todos los requisitos. - El resultado final se guarda en la base de datos. - Los participantes pueden ver el estado de validación. - Si la quedada no cumple requisitos, se marca como “no válida”. - Si ocurre error, se informa al usuario.</t>
-  </si>
-  <si>
-    <t>- El organizador puede marcar ciertos participantes como “MVP”. - Solo puede seleccionar usuarios que asistieron. - El sistema evita duplicar premios. - Al seleccionar un MVP, se actualiza en la base de datos. - Si ocurre error, se muestra mensaje.</t>
-  </si>
-  <si>
-    <t>- Los participantes pueden ver quién ha sido elegido como MVP. - Se muestra en la pantalla de resumen final de la quedada. - Si no hay MVP asignados, se indica. - Los datos coinciden con la información guardada. - Si ocurre error de carga, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- El organizador puede añadir comentarios finales a la quedada. - El campo de comentarios valida longitud mínima. - Los comentarios se guardan correctamente. - Los participantes pueden leerlos en la vista de resultados. - Si ocurre error, aparece aviso.</t>
-  </si>
-  <si>
-    <t>- Los comentarios finales se muestran en un panel dedicado. - El texto se muestra completo incluso si es largo. - Si no hay comentarios, se indica. - Los comentarios se cargan desde la base de datos. - Si hay fallo de carga, aparece mensaje.</t>
-  </si>
-  <si>
-    <t>- Tras finalizar la quedada, se muestra una pantalla de resumen. - La pantalla incluye puntuaciones, MVP y comentarios finales. - Los datos se muestran de forma ordenada y clara. - Si falta información, se indica de forma visual. - Si ocurre error, se notifica.</t>
-  </si>
-  <si>
-    <t>- El sistema guarda la fecha y hora en que la quedada se validó o marcó como no válida. - Esta información queda disponible en el historial. - Los datos son editables solo por el sistema, no por usuarios. - La fecha se registra con zona horaria correcta. - Si ocurre error al guardar, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- El usuario puede filtrar quedadas por estado: válida, no válida, pendiente. - El filtro aplica cambios instantáneos en la lista. - Se pueden combinar filtros con búsqueda por nombre. - Si no hay resultados, se muestra mensaje. - Si el filtro falla, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- Los administradores pueden ver una sección con todas las quedadas no válidas. - Se muestran ordenadas por fecha o relevancia. - Cada quedada muestra información clave como motivo de no validez. - Si no existe ninguna, se indica. - Si ocurre error de carga, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- El usuario puede marcar quedadas como favoritas. - Al pulsar el icono correspondiente, se guarda en su lista personal. - El icono cambia de estado (activado/desactivado). - Las favoritas aparecen en una sección dedicada. - Si ocurre error al guardar, se muestra aviso.</t>
-  </si>
-  <si>
-    <t>- La lista de favoritas muestra título, fecha y ubicación de cada quedada. - El usuario puede acceder a los detalles desde esta lista. - Si no hay favoritas, se muestra mensaje. - Si ocurre error al cargarlas, aparece aviso. - El usuario puede quitar quedadas de favoritos directamente desde la lista.</t>
   </si>
   <si>
     <t xml:space="preserve"> - El usuario autenticado visualiza su nombre, correo y foto al abrir el perfil.
@@ -6723,6 +6672,122 @@
  - El sistema filtra usuarios conforme se escribe.
  - Si no hay resultados, se muestra un mensaje informativo.
  - Si ocurre error al buscar, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El creador/administrador visualiza un botón de eliminar quedada.
+ - El botón solo aparece en las quedadas que administra.
+ - Al pulsarlo se solicita confirmación antes de eliminar.
+ - Tras confirmar, la quedada se elimina correctamente.
+ - Si ocurre error, se muestra un mensaje informativo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestra a los participantes un botón de denegar eliminación cuando otro usuario quiere eliminar la quedada.
+ - El botón permite registrar la denegación.
+ - Si un participante deniega, la quedada no se elimina.
+ - Los participantes reciben una actualización del estado.
+ - Si ocurre error al registrar la acción, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestra a los participantes un botón de aceptar eliminación cuando la quedada está pendiente de ser eliminada.
+ - El botón permite registrar la aceptación.
+ - La quedada solo puede eliminarse si los usuarios la aceptan.
+ - La interfaz refleja el estado actualizado.
+ - Si ocurre error, se muestra mensaje de aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El participante ve un botón de negar puntuación asignada a la quedada.
+ - Al pulsarlo, se registra la negación de la puntuación.
+ - La puntuación queda marcada como incorrecta.
+ - Se muestra notificación del cambio de estado.
+ - Si ocurre error al registrar, se informa al usuario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestra un botón de confirmar puntuación al participante.
+ - Al pulsarlo, se registra su confirmación.
+ - La puntuación queda marcada como aceptada.
+ - El sistema actualiza la información para todos los participantes.
+ - Si ocurre error, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El usuario puede visualizar su puntuación competitiva.
+ - La información se muestra de forma clara y accesible.
+ - Si ocurre error al cargar, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestra un formulario con filtros de detalles competitivos.
+ - El usuario puede seleccionar deporte u otros criterios.
+ - La información mostrada cambia según los filtros aplicados.
+ - Los filtros pueden activarse o modificarse sin recargar la página.
+ - Si ocurre error en la carga, se avisa al usuario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El usuario puede ver su ratio de victorias/derrotas.
+ - El ratio corresponde al deporte filtrado.
+ - La información se calcula correctamente según sus quedadas.
+ - Los datos se actualizan cuando se cambian filtros.
+ - Si ocurre error, se muestra mensaje.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El usuario puede ver el total de quedadas competitivas perdidas.
+ - El total corresponde al deporte filtrado.
+ - Los datos coinciden con el historial competitivo del usuario.
+ - La información se actualiza al modificar filtros.
+ - Si ocurre error, se notifica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El usuario puede ver su total de quedadas competitivas empatadas.
+ - El número mostrado corresponde al deporte filtrado.
+ - Los datos coinciden con el registro competitivo.
+ - Se actualizan al cambiar filtros.
+ - Si ocurre error, se muestra un aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El usuario puede ver su total de quedadas competitivas ganadas.
+ - Los datos corresponden al deporte seleccionado.
+ - La información es coherente con su historial.
+ - Se actualiza al modificar filtros.
+ - Si ocurre error, se informa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El usuario ve una lista de quedadas competitivas en las que ha participado.
+ - Cada quedada muestra sus detalles competitivos.
+ - La lista corresponde al deporte filtrado.
+ - Los datos se actualizan según el filtro.
+ - Si ocurre error, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El usuario puede visualizar el perfil de otro usuario.
+ - El perfil muestra información relevante del usuario.
+ - Desde el perfil se pueden realizar acciones como reportar o añadir amigo.
+ - La información se carga correctamente al acceder.
+ - Si ocurre error, se informa al usuario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - En los usuarios visibles aparece un botón de “Añadir amigo”.
+ - Al pulsarlo, el usuario se añade a la lista de amigos.
+ - El sistema confirma correctamente la acción.
+ - El botón cambia de estado si el usuario ya es amigo.
+ - Si ocurre error, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Los usuarios mostrados incluyen un botón de “Ver perfil”.
+ - Al pulsarlo, se abre la página de perfil del usuario.
+ - La información se muestra correctamente.
+ - El botón está disponible en todas las vistas donde aparece un usuario.
+ - Si ocurre error, se informa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El usuario puede acceder a su lista de amistades.
+ - La lista muestra todos los usuarios añadidos como amigos.
+ - Los datos se actualizan correctamente.
+ - Si ocurre error al cargar la lista, se muestra aviso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestran filtros para buscar entre los amigos añadidos.
+ - El usuario puede seleccionar un criterio de búsqueda.
+ - Los resultados se actualizan según el filtro aplicado.
+ - La búsqueda funciona según los criterios disponibles.
+ - Si ocurre error, se muestra aviso.</t>
   </si>
 </sst>
 </file>
@@ -6859,7 +6924,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -6896,9 +6961,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6910,6 +6972,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -76089,1267 +76160,1124 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="48.140625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="69.5703125" customWidth="1"/>
     <col min="6" max="6" width="56.42578125" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="82.7109375" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" customWidth="1"/>
+    <col min="10" max="10" width="97.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>1878</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="25" t="s">
         <v>1248</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="21" t="s">
         <v>1879</v>
       </c>
-      <c r="E1" s="23" t="s">
-        <v>1878</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+    </row>
+    <row r="2" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1880</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="26" t="s">
         <v>1868</v>
       </c>
-      <c r="C2" s="24" t="s">
-        <v>1986</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>1880</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="27" t="s">
+        <v>1969</v>
+      </c>
+      <c r="E2" s="24"/>
+    </row>
+    <row r="3" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>1881</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="26" t="s">
         <v>1159</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="27" t="s">
         <v>1968</v>
       </c>
-      <c r="E3" s="25" t="s">
-        <v>1881</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E3" s="24"/>
+    </row>
+    <row r="4" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>1882</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="26" t="s">
         <v>1168</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>1987</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>1882</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="27" t="s">
+        <v>1970</v>
+      </c>
+      <c r="E4" s="24"/>
+    </row>
+    <row r="5" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>1883</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="26" t="s">
         <v>1171</v>
       </c>
-      <c r="C5" s="24" t="s">
-        <v>1988</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>1883</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="27" t="s">
+        <v>1971</v>
+      </c>
+      <c r="E5" s="24"/>
+    </row>
+    <row r="6" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>1884</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="26" t="s">
         <v>1155</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>1989</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>1884</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="27" t="s">
+        <v>1972</v>
+      </c>
+      <c r="E6" s="24"/>
+    </row>
+    <row r="7" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>1885</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="26" t="s">
         <v>1873</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>1990</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="27" t="s">
+        <v>1973</v>
+      </c>
+      <c r="E7" s="24"/>
+    </row>
+    <row r="8" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>1886</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="26" t="s">
         <v>1671</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>1991</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>1886</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="27" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E8" s="24"/>
+    </row>
+    <row r="9" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>1887</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="26" t="s">
         <v>1672</v>
       </c>
-      <c r="C9" s="24" t="s">
-        <v>1992</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>1887</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="27" t="s">
+        <v>1975</v>
+      </c>
+      <c r="E9" s="24"/>
+    </row>
+    <row r="10" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>1888</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="26" t="s">
         <v>1670</v>
       </c>
-      <c r="C10" s="24" t="s">
-        <v>1993</v>
-      </c>
-      <c r="E10" s="25" t="s">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="27" t="s">
+        <v>1976</v>
+      </c>
+      <c r="E10" s="24"/>
+    </row>
+    <row r="11" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>1889</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="26" t="s">
         <v>1794</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>1994</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>1889</v>
-      </c>
+      <c r="C11" s="27" t="s">
+        <v>1977</v>
+      </c>
+      <c r="E11" s="24"/>
     </row>
     <row r="12" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>1890</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="26" t="s">
         <v>1650</v>
       </c>
-      <c r="C12" s="24" t="s">
-        <v>1995</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>1890</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="27" t="s">
+        <v>1978</v>
+      </c>
+      <c r="E12" s="24"/>
+    </row>
+    <row r="13" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>1891</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="26" t="s">
         <v>1103</v>
       </c>
-      <c r="C13" s="24" t="s">
-        <v>1996</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>1891</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="27" t="s">
+        <v>1979</v>
+      </c>
+      <c r="E13" s="24"/>
+    </row>
+    <row r="14" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>1892</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="26" t="s">
         <v>1874</v>
       </c>
-      <c r="C14" s="24" t="s">
-        <v>1997</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>1892</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="27" t="s">
+        <v>1980</v>
+      </c>
+      <c r="E14" s="24"/>
+    </row>
+    <row r="15" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>1893</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="26" t="s">
         <v>1105</v>
       </c>
-      <c r="C15" s="24" t="s">
-        <v>1998</v>
-      </c>
-      <c r="E15" s="25" t="s">
-        <v>1893</v>
-      </c>
+      <c r="C15" s="27" t="s">
+        <v>1981</v>
+      </c>
+      <c r="E15" s="24"/>
     </row>
     <row r="16" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>1894</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="26" t="s">
         <v>1669</v>
       </c>
-      <c r="C16" s="24" t="s">
-        <v>1999</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>1894</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="27" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E16" s="24"/>
+    </row>
+    <row r="17" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>1895</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="26" t="s">
         <v>1727</v>
       </c>
-      <c r="C17" s="24" t="s">
-        <v>2000</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="27" t="s">
+        <v>1983</v>
+      </c>
+      <c r="E17" s="24"/>
+    </row>
+    <row r="18" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>1896</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="26" t="s">
         <v>1151</v>
       </c>
-      <c r="C18" s="24" t="s">
-        <v>2001</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>1896</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="27" t="s">
+        <v>1984</v>
+      </c>
+      <c r="E18" s="24"/>
+    </row>
+    <row r="19" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>1897</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="26" t="s">
         <v>1726</v>
       </c>
-      <c r="C19" s="24" t="s">
-        <v>2002</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>1897</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="27" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E19" s="24"/>
+    </row>
+    <row r="20" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>1898</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="26" t="s">
         <v>1148</v>
       </c>
-      <c r="C20" s="24" t="s">
-        <v>2003</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>1898</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C20" s="27" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E20" s="24"/>
+    </row>
+    <row r="21" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
         <v>1899</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="26" t="s">
         <v>1146</v>
       </c>
-      <c r="C21" s="24" t="s">
-        <v>2004</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>1899</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="27" t="s">
+        <v>1987</v>
+      </c>
+      <c r="E21" s="24"/>
+    </row>
+    <row r="22" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
         <v>1900</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="26" t="s">
         <v>1665</v>
       </c>
-      <c r="C22" s="24" t="s">
-        <v>2005</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="27" t="s">
+        <v>1988</v>
+      </c>
+      <c r="E22" s="24"/>
+    </row>
+    <row r="23" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
         <v>1901</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="26" t="s">
         <v>1660</v>
       </c>
-      <c r="C23" s="24" t="s">
-        <v>2006</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>1901</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C23" s="27" t="s">
+        <v>1989</v>
+      </c>
+      <c r="E23" s="24"/>
+    </row>
+    <row r="24" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
         <v>1902</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="26" t="s">
         <v>1132</v>
       </c>
-      <c r="C24" s="24" t="s">
-        <v>2007</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>1902</v>
-      </c>
+      <c r="C24" s="27" t="s">
+        <v>1990</v>
+      </c>
+      <c r="E24" s="24"/>
     </row>
     <row r="25" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
         <v>1903</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="26" t="s">
         <v>1659</v>
       </c>
-      <c r="C25" s="24" t="s">
-        <v>2008</v>
-      </c>
-      <c r="E25" s="25" t="s">
-        <v>1903</v>
-      </c>
+      <c r="C25" s="27" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E25" s="24"/>
     </row>
     <row r="26" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
         <v>1904</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="26" t="s">
         <v>1658</v>
       </c>
-      <c r="C26" s="24" t="s">
-        <v>2009</v>
-      </c>
-      <c r="E26" s="25" t="s">
-        <v>1904</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C26" s="27" t="s">
+        <v>1992</v>
+      </c>
+      <c r="E26" s="24"/>
+    </row>
+    <row r="27" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
         <v>1905</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="26" t="s">
         <v>1126</v>
       </c>
-      <c r="C27" s="24" t="s">
-        <v>2010</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>1905</v>
-      </c>
+      <c r="C27" s="27" t="s">
+        <v>1993</v>
+      </c>
+      <c r="E27" s="24"/>
     </row>
     <row r="28" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>1906</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="26" t="s">
         <v>1657</v>
       </c>
-      <c r="C28" s="24" t="s">
-        <v>2011</v>
-      </c>
-      <c r="E28" s="25" t="s">
-        <v>1906</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C28" s="27" t="s">
+        <v>1994</v>
+      </c>
+      <c r="E28" s="24"/>
+    </row>
+    <row r="29" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
         <v>1907</v>
       </c>
-      <c r="B29" s="20" t="s">
+      <c r="B29" s="26" t="s">
         <v>1228</v>
       </c>
-      <c r="C29" s="24" t="s">
-        <v>2012</v>
-      </c>
-      <c r="E29" s="25" t="s">
-        <v>1907</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C29" s="27" t="s">
+        <v>1995</v>
+      </c>
+      <c r="E29" s="24"/>
+    </row>
+    <row r="30" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
         <v>1908</v>
       </c>
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="26" t="s">
         <v>1872</v>
       </c>
-      <c r="C30" s="24" t="s">
-        <v>2013</v>
-      </c>
-      <c r="E30" s="25" t="s">
-        <v>1908</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C30" s="27" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E30" s="24"/>
+    </row>
+    <row r="31" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
         <v>1909</v>
       </c>
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="26" t="s">
         <v>1663</v>
       </c>
-      <c r="C31" s="24" t="s">
-        <v>2014</v>
-      </c>
-      <c r="E31" s="25" t="s">
-        <v>1909</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C31" s="27" t="s">
+        <v>1997</v>
+      </c>
+      <c r="E31" s="24"/>
+    </row>
+    <row r="32" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
         <v>1910</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="26" t="s">
         <v>1229</v>
       </c>
-      <c r="C32" s="24" t="s">
-        <v>2015</v>
-      </c>
-      <c r="E32" s="25" t="s">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="27" t="s">
+        <v>1998</v>
+      </c>
+      <c r="E32" s="24"/>
+    </row>
+    <row r="33" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
         <v>1911</v>
       </c>
-      <c r="B33" s="20" t="s">
+      <c r="B33" s="26" t="s">
         <v>1655</v>
       </c>
-      <c r="C33" s="24" t="s">
-        <v>2016</v>
-      </c>
-      <c r="E33" s="25" t="s">
-        <v>1911</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="27" t="s">
+        <v>1999</v>
+      </c>
+      <c r="E33" s="24"/>
+    </row>
+    <row r="34" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
         <v>1912</v>
       </c>
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="26" t="s">
         <v>1656</v>
       </c>
-      <c r="C34" s="24" t="s">
-        <v>2017</v>
-      </c>
-      <c r="E34" s="25" t="s">
-        <v>1912</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C34" s="27" t="s">
+        <v>2000</v>
+      </c>
+      <c r="E34" s="24"/>
+    </row>
+    <row r="35" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19" t="s">
         <v>1913</v>
       </c>
-      <c r="B35" s="20" t="s">
+      <c r="B35" s="26" t="s">
         <v>1117</v>
       </c>
-      <c r="C35" s="24" t="s">
-        <v>2018</v>
-      </c>
-      <c r="E35" s="25" t="s">
-        <v>1913</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="27" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E35" s="24"/>
+    </row>
+    <row r="36" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19" t="s">
         <v>1914</v>
       </c>
-      <c r="B36" s="20" t="s">
+      <c r="B36" s="26" t="s">
         <v>1870</v>
       </c>
-      <c r="C36" s="24" t="s">
-        <v>2019</v>
-      </c>
-      <c r="E36" s="25" t="s">
-        <v>1914</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="27" t="s">
+        <v>2002</v>
+      </c>
+      <c r="E36" s="24"/>
+    </row>
+    <row r="37" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19" t="s">
         <v>1915</v>
       </c>
-      <c r="B37" s="20" t="s">
+      <c r="B37" s="26" t="s">
         <v>1871</v>
       </c>
-      <c r="C37" s="24" t="s">
-        <v>2020</v>
-      </c>
-      <c r="E37" s="25" t="s">
-        <v>1915</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="27" t="s">
+        <v>2003</v>
+      </c>
+      <c r="E37" s="24"/>
+    </row>
+    <row r="38" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="19" t="s">
         <v>1916</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="26" t="s">
         <v>1792</v>
       </c>
-      <c r="C38" s="24" t="s">
-        <v>2021</v>
-      </c>
-      <c r="E38" s="25" t="s">
-        <v>1916</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="27" t="s">
+        <v>2004</v>
+      </c>
+      <c r="E38" s="24"/>
+    </row>
+    <row r="39" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19" t="s">
         <v>1917</v>
       </c>
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="26" t="s">
         <v>1637</v>
       </c>
-      <c r="C39" s="24" t="s">
-        <v>2022</v>
-      </c>
-      <c r="E39" s="25" t="s">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="27" t="s">
+        <v>2005</v>
+      </c>
+      <c r="E39" s="24"/>
+    </row>
+    <row r="40" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19" t="s">
         <v>1918</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="26" t="s">
         <v>1661</v>
       </c>
-      <c r="C40" s="24" t="s">
-        <v>2023</v>
-      </c>
-      <c r="E40" s="25" t="s">
-        <v>1918</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="27" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E40" s="24"/>
+    </row>
+    <row r="41" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
         <v>1919</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="26" t="s">
         <v>1795</v>
       </c>
-      <c r="C41" s="24" t="s">
-        <v>2024</v>
-      </c>
-      <c r="E41" s="25" t="s">
-        <v>1919</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="27" t="s">
+        <v>2007</v>
+      </c>
+      <c r="E41" s="24"/>
+    </row>
+    <row r="42" spans="1:10" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="19" t="s">
         <v>1920</v>
       </c>
-      <c r="B42" s="20" t="s">
+      <c r="B42" s="26" t="s">
         <v>1244</v>
       </c>
-      <c r="C42" s="24" t="s">
-        <v>2025</v>
-      </c>
-      <c r="E42" s="25" t="s">
-        <v>1920</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="27" t="s">
+        <v>2008</v>
+      </c>
+      <c r="E42" s="24"/>
+    </row>
+    <row r="43" spans="1:10" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="19" t="s">
         <v>1921</v>
       </c>
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="26" t="s">
         <v>1869</v>
       </c>
-      <c r="C43" s="24" t="s">
-        <v>2026</v>
-      </c>
-      <c r="E43" s="25" t="s">
-        <v>1921</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C43" s="27" t="s">
+        <v>2009</v>
+      </c>
+      <c r="E43" s="24"/>
+    </row>
+    <row r="44" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="19" t="s">
         <v>1922</v>
       </c>
-      <c r="B44" s="20" t="s">
+      <c r="B44" s="26" t="s">
         <v>1662</v>
       </c>
-      <c r="C44" s="24" t="s">
-        <v>2027</v>
-      </c>
-      <c r="E44" s="25" t="s">
-        <v>1922</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C44" s="27" t="s">
+        <v>2010</v>
+      </c>
+      <c r="E44" s="24"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+    </row>
+    <row r="45" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="19" t="s">
         <v>1923</v>
       </c>
-      <c r="B45" s="20" t="s">
+      <c r="B45" s="26" t="s">
         <v>1203</v>
       </c>
-      <c r="E45" s="25" t="s">
-        <v>1923</v>
-      </c>
-      <c r="F45" s="24" t="s">
-        <v>1969</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C45" s="27" t="s">
+        <v>2039</v>
+      </c>
+      <c r="E45" s="24"/>
+      <c r="I45" s="24"/>
+      <c r="J45" s="23"/>
+    </row>
+    <row r="46" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="19" t="s">
         <v>1924</v>
       </c>
-      <c r="B46" s="20" t="s">
+      <c r="B46" s="26" t="s">
         <v>1201</v>
       </c>
-      <c r="E46" s="25" t="s">
-        <v>1924</v>
-      </c>
-      <c r="F46" s="24" t="s">
-        <v>1970</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C46" s="27" t="s">
+        <v>2040</v>
+      </c>
+      <c r="E46" s="24"/>
+      <c r="I46" s="24"/>
+      <c r="J46" s="23"/>
+    </row>
+    <row r="47" spans="1:10" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="19" t="s">
         <v>1925</v>
       </c>
-      <c r="B47" s="20" t="s">
+      <c r="B47" s="26" t="s">
         <v>1202</v>
       </c>
-      <c r="E47" s="25" t="s">
-        <v>1925</v>
-      </c>
-      <c r="F47" s="24" t="s">
-        <v>1971</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C47" s="27" t="s">
+        <v>2041</v>
+      </c>
+      <c r="E47" s="24"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="23"/>
+    </row>
+    <row r="48" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="19" t="s">
         <v>1926</v>
       </c>
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="26" t="s">
         <v>1652</v>
       </c>
-      <c r="E48" s="25" t="s">
-        <v>1926</v>
-      </c>
-      <c r="F48" s="24" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C48" s="27" t="s">
+        <v>2042</v>
+      </c>
+      <c r="E48" s="24"/>
+      <c r="I48" s="24"/>
+      <c r="J48" s="23"/>
+    </row>
+    <row r="49" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="19" t="s">
         <v>1927</v>
       </c>
-      <c r="B49" s="20" t="s">
+      <c r="B49" s="26" t="s">
         <v>1654</v>
       </c>
-      <c r="E49" s="25" t="s">
-        <v>1927</v>
-      </c>
-      <c r="F49" s="24" t="s">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="27" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E49" s="24"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="23"/>
+    </row>
+    <row r="50" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="19" t="s">
         <v>1928</v>
       </c>
-      <c r="B50" s="20" t="s">
+      <c r="B50" s="26" t="s">
         <v>1648</v>
       </c>
-      <c r="E50" s="25" t="s">
-        <v>1928</v>
-      </c>
-      <c r="F50" s="24" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C50" s="27" t="s">
+        <v>2044</v>
+      </c>
+      <c r="E50" s="24"/>
+      <c r="I50" s="24"/>
+      <c r="J50" s="23"/>
+    </row>
+    <row r="51" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="19" t="s">
         <v>1929</v>
       </c>
-      <c r="B51" s="20" t="s">
+      <c r="B51" s="26" t="s">
         <v>1647</v>
       </c>
-      <c r="E51" s="25" t="s">
-        <v>1929</v>
-      </c>
-      <c r="F51" s="24" t="s">
-        <v>1975</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C51" s="27" t="s">
+        <v>2045</v>
+      </c>
+      <c r="E51" s="24"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="23"/>
+    </row>
+    <row r="52" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="19" t="s">
         <v>1930</v>
       </c>
-      <c r="B52" s="20" t="s">
+      <c r="B52" s="26" t="s">
         <v>1092</v>
       </c>
-      <c r="E52" s="25" t="s">
-        <v>1930</v>
-      </c>
-      <c r="F52" s="24" t="s">
-        <v>1976</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="27" t="s">
+        <v>2046</v>
+      </c>
+      <c r="E52" s="24"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="23"/>
+    </row>
+    <row r="53" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="19" t="s">
         <v>1931</v>
       </c>
-      <c r="B53" s="20" t="s">
+      <c r="B53" s="26" t="s">
         <v>1094</v>
       </c>
-      <c r="E53" s="25" t="s">
-        <v>1931</v>
-      </c>
-      <c r="F53" s="24" t="s">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C53" s="27" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E53" s="24"/>
+      <c r="I53" s="24"/>
+      <c r="J53" s="23"/>
+    </row>
+    <row r="54" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="19" t="s">
         <v>1932</v>
       </c>
-      <c r="B54" s="20" t="s">
+      <c r="B54" s="26" t="s">
         <v>1096</v>
       </c>
-      <c r="E54" s="25" t="s">
-        <v>1932</v>
-      </c>
-      <c r="F54" s="24" t="s">
-        <v>1978</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C54" s="27" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E54" s="24"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="23"/>
+    </row>
+    <row r="55" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="19" t="s">
         <v>1933</v>
       </c>
-      <c r="B55" s="20" t="s">
+      <c r="B55" s="26" t="s">
         <v>1098</v>
       </c>
-      <c r="E55" s="25" t="s">
-        <v>1933</v>
-      </c>
-      <c r="F55" s="24" t="s">
-        <v>1979</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C55" s="27" t="s">
+        <v>2049</v>
+      </c>
+      <c r="E55" s="24"/>
+      <c r="I55" s="24"/>
+      <c r="J55" s="23"/>
+    </row>
+    <row r="56" spans="1:10" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="19" t="s">
         <v>1934</v>
       </c>
-      <c r="B56" s="20" t="s">
+      <c r="B56" s="26" t="s">
         <v>1090</v>
       </c>
-      <c r="E56" s="25" t="s">
-        <v>1934</v>
-      </c>
-      <c r="F56" s="24" t="s">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C56" s="27" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E56" s="24"/>
+      <c r="I56" s="24"/>
+      <c r="J56" s="23"/>
+    </row>
+    <row r="57" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="19" t="s">
         <v>1935</v>
       </c>
-      <c r="B57" s="20" t="s">
+      <c r="B57" s="26" t="s">
         <v>1861</v>
       </c>
-      <c r="E57" s="25" t="s">
-        <v>1935</v>
-      </c>
-      <c r="F57" s="24" t="s">
-        <v>1981</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C57" s="27" t="s">
+        <v>2051</v>
+      </c>
+      <c r="E57" s="24"/>
+      <c r="I57" s="24"/>
+      <c r="J57" s="23"/>
+    </row>
+    <row r="58" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="19" t="s">
         <v>1936</v>
       </c>
-      <c r="B58" s="20" t="s">
+      <c r="B58" s="26" t="s">
         <v>1787</v>
       </c>
-      <c r="E58" s="25" t="s">
-        <v>1936</v>
-      </c>
-      <c r="F58" s="24" t="s">
-        <v>1982</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C58" s="27" t="s">
+        <v>2052</v>
+      </c>
+      <c r="E58" s="24"/>
+      <c r="I58" s="24"/>
+      <c r="J58" s="23"/>
+    </row>
+    <row r="59" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="19" t="s">
         <v>1937</v>
       </c>
-      <c r="B59" s="20" t="s">
+      <c r="B59" s="26" t="s">
         <v>1624</v>
       </c>
-      <c r="E59" s="25" t="s">
-        <v>1937</v>
-      </c>
-      <c r="F59" s="24" t="s">
-        <v>1983</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C59" s="27" t="s">
+        <v>2053</v>
+      </c>
+      <c r="E59" s="24"/>
+      <c r="I59" s="24"/>
+      <c r="J59" s="23"/>
+    </row>
+    <row r="60" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="19" t="s">
         <v>1938</v>
       </c>
-      <c r="B60" s="20" t="s">
+      <c r="B60" s="26" t="s">
         <v>1211</v>
       </c>
-      <c r="E60" s="25" t="s">
-        <v>1938</v>
-      </c>
-      <c r="F60" s="24" t="s">
-        <v>1984</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C60" s="27" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E60" s="24"/>
+      <c r="I60" s="24"/>
+      <c r="J60" s="23"/>
+    </row>
+    <row r="61" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="19" t="s">
         <v>1939</v>
       </c>
-      <c r="B61" s="20" t="s">
+      <c r="B61" s="26" t="s">
         <v>1209</v>
       </c>
-      <c r="E61" s="25" t="s">
-        <v>1939</v>
-      </c>
-      <c r="F61" s="24" t="s">
-        <v>1985</v>
-      </c>
-      <c r="G61" s="23"/>
-      <c r="H61" s="23"/>
-    </row>
-    <row r="62" spans="1:8" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C61" s="27" t="s">
+        <v>2055</v>
+      </c>
+      <c r="E61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="23"/>
+    </row>
+    <row r="62" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="19" t="s">
         <v>1940</v>
       </c>
-      <c r="B62" s="20" t="s">
+      <c r="B62" s="26" t="s">
         <v>1210</v>
       </c>
-      <c r="C62" s="24" t="s">
-        <v>2055</v>
-      </c>
-      <c r="E62" s="25" t="s">
-        <v>1940</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C62" s="27" t="s">
+        <v>2038</v>
+      </c>
+      <c r="E62" s="24"/>
+    </row>
+    <row r="63" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="19" t="s">
         <v>1941</v>
       </c>
-      <c r="B63" s="20" t="s">
+      <c r="B63" s="26" t="s">
         <v>1208</v>
       </c>
-      <c r="C63" s="24" t="s">
-        <v>2054</v>
-      </c>
-      <c r="E63" s="25" t="s">
-        <v>1941</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C63" s="27" t="s">
+        <v>2037</v>
+      </c>
+      <c r="E63" s="24"/>
+    </row>
+    <row r="64" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="19" t="s">
         <v>1942</v>
       </c>
-      <c r="B64" s="20" t="s">
+      <c r="B64" s="26" t="s">
         <v>1642</v>
       </c>
-      <c r="C64" s="24" t="s">
-        <v>2053</v>
-      </c>
-      <c r="E64" s="25" t="s">
-        <v>1942</v>
-      </c>
+      <c r="C64" s="27" t="s">
+        <v>2036</v>
+      </c>
+      <c r="E64" s="24"/>
     </row>
     <row r="65" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="19" t="s">
         <v>1943</v>
       </c>
-      <c r="B65" s="20" t="s">
+      <c r="B65" s="26" t="s">
         <v>1643</v>
       </c>
-      <c r="C65" s="24" t="s">
-        <v>2052</v>
-      </c>
-      <c r="E65" s="25" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C65" s="27" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E65" s="24"/>
+    </row>
+    <row r="66" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="19" t="s">
         <v>1944</v>
       </c>
-      <c r="B66" s="20" t="s">
+      <c r="B66" s="26" t="s">
         <v>1646</v>
       </c>
-      <c r="C66" s="24" t="s">
-        <v>2051</v>
-      </c>
-      <c r="E66" s="25" t="s">
-        <v>1944</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C66" s="27" t="s">
+        <v>2034</v>
+      </c>
+      <c r="E66" s="24"/>
+    </row>
+    <row r="67" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="19" t="s">
         <v>1945</v>
       </c>
-      <c r="B67" s="20" t="s">
+      <c r="B67" s="26" t="s">
         <v>1080</v>
       </c>
-      <c r="C67" s="24" t="s">
-        <v>2050</v>
-      </c>
-      <c r="E67" s="25" t="s">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C67" s="27" t="s">
+        <v>2033</v>
+      </c>
+      <c r="E67" s="24"/>
+    </row>
+    <row r="68" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="19" t="s">
         <v>1946</v>
       </c>
-      <c r="B68" s="20" t="s">
+      <c r="B68" s="26" t="s">
         <v>1073</v>
       </c>
-      <c r="C68" s="24" t="s">
-        <v>2049</v>
-      </c>
-      <c r="E68" s="25" t="s">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C68" s="27" t="s">
+        <v>2032</v>
+      </c>
+      <c r="E68" s="24"/>
+    </row>
+    <row r="69" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="19" t="s">
         <v>1947</v>
       </c>
-      <c r="B69" s="20" t="s">
+      <c r="B69" s="26" t="s">
         <v>1866</v>
       </c>
-      <c r="C69" s="24" t="s">
-        <v>2048</v>
-      </c>
-      <c r="E69" s="25" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C69" s="27" t="s">
+        <v>2031</v>
+      </c>
+      <c r="E69" s="24"/>
+    </row>
+    <row r="70" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="19" t="s">
         <v>1948</v>
       </c>
-      <c r="B70" s="20" t="s">
+      <c r="B70" s="26" t="s">
         <v>1724</v>
       </c>
-      <c r="C70" s="24" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E70" s="25" t="s">
-        <v>1948</v>
-      </c>
+      <c r="C70" s="27" t="s">
+        <v>2030</v>
+      </c>
+      <c r="E70" s="24"/>
     </row>
     <row r="71" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="19" t="s">
         <v>1949</v>
       </c>
-      <c r="B71" s="20" t="s">
+      <c r="B71" s="26" t="s">
         <v>1723</v>
       </c>
-      <c r="C71" s="24" t="s">
-        <v>2046</v>
-      </c>
-      <c r="E71" s="25" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C71" s="27" t="s">
+        <v>2029</v>
+      </c>
+      <c r="E71" s="24"/>
+    </row>
+    <row r="72" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="19" t="s">
         <v>1950</v>
       </c>
-      <c r="B72" s="20" t="s">
+      <c r="B72" s="26" t="s">
         <v>1635</v>
       </c>
-      <c r="C72" s="24" t="s">
-        <v>2045</v>
-      </c>
-      <c r="E72" s="25" t="s">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="27" t="s">
+        <v>2028</v>
+      </c>
+      <c r="E72" s="24"/>
+    </row>
+    <row r="73" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="19" t="s">
         <v>1951</v>
       </c>
-      <c r="B73" s="20" t="s">
+      <c r="B73" s="26" t="s">
         <v>1633</v>
       </c>
-      <c r="C73" s="24" t="s">
-        <v>2044</v>
-      </c>
-      <c r="E73" s="25" t="s">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C73" s="27" t="s">
+        <v>2027</v>
+      </c>
+      <c r="E73" s="24"/>
+    </row>
+    <row r="74" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="19" t="s">
         <v>1952</v>
       </c>
-      <c r="B74" s="20" t="s">
+      <c r="B74" s="26" t="s">
         <v>1793</v>
       </c>
-      <c r="C74" s="24" t="s">
-        <v>2043</v>
-      </c>
-      <c r="E74" s="25" t="s">
-        <v>1952</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C74" s="27" t="s">
+        <v>2026</v>
+      </c>
+      <c r="E74" s="24"/>
+    </row>
+    <row r="75" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="19" t="s">
         <v>1953</v>
       </c>
-      <c r="B75" s="20" t="s">
+      <c r="B75" s="26" t="s">
         <v>1058</v>
       </c>
-      <c r="C75" s="24" t="s">
-        <v>2042</v>
-      </c>
-      <c r="E75" s="25" t="s">
-        <v>1953</v>
-      </c>
+      <c r="C75" s="27" t="s">
+        <v>2025</v>
+      </c>
+      <c r="E75" s="24"/>
     </row>
     <row r="76" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="19" t="s">
         <v>1954</v>
       </c>
-      <c r="B76" s="20" t="s">
+      <c r="B76" s="26" t="s">
         <v>1639</v>
       </c>
-      <c r="C76" s="24" t="s">
-        <v>2041</v>
-      </c>
-      <c r="E76" s="25" t="s">
-        <v>1954</v>
-      </c>
+      <c r="C76" s="27" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E76" s="24"/>
     </row>
     <row r="77" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="19" t="s">
         <v>1955</v>
       </c>
-      <c r="B77" s="20" t="s">
+      <c r="B77" s="26" t="s">
         <v>1640</v>
       </c>
-      <c r="C77" s="24" t="s">
-        <v>2040</v>
-      </c>
-      <c r="E77" s="25" t="s">
-        <v>1955</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="27" t="s">
+        <v>2023</v>
+      </c>
+      <c r="E77" s="24"/>
+    </row>
+    <row r="78" spans="1:5" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="19" t="s">
         <v>1956</v>
       </c>
-      <c r="B78" s="20" t="s">
+      <c r="B78" s="26" t="s">
         <v>1641</v>
       </c>
-      <c r="C78" s="24" t="s">
-        <v>2039</v>
-      </c>
-      <c r="E78" s="25" t="s">
-        <v>1956</v>
-      </c>
+      <c r="C78" s="27" t="s">
+        <v>2022</v>
+      </c>
+      <c r="E78" s="24"/>
     </row>
     <row r="79" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="19" t="s">
         <v>1957</v>
       </c>
-      <c r="B79" s="20" t="s">
+      <c r="B79" s="26" t="s">
         <v>1207</v>
       </c>
-      <c r="C79" s="24" t="s">
-        <v>2038</v>
-      </c>
-      <c r="E79" s="25" t="s">
-        <v>1957</v>
-      </c>
+      <c r="C79" s="27" t="s">
+        <v>2021</v>
+      </c>
+      <c r="E79" s="24"/>
     </row>
     <row r="80" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="19" t="s">
         <v>1958</v>
       </c>
-      <c r="B80" s="20" t="s">
+      <c r="B80" s="26" t="s">
         <v>1204</v>
       </c>
-      <c r="C80" s="24" t="s">
-        <v>2037</v>
-      </c>
-      <c r="E80" s="25" t="s">
-        <v>1958</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C80" s="27" t="s">
+        <v>2020</v>
+      </c>
+      <c r="E80" s="24"/>
+    </row>
+    <row r="81" spans="1:8" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="19" t="s">
         <v>1959</v>
       </c>
-      <c r="B81" s="20" t="s">
+      <c r="B81" s="26" t="s">
         <v>1205</v>
       </c>
-      <c r="C81" s="24" t="s">
-        <v>2036</v>
-      </c>
-      <c r="E81" s="25" t="s">
-        <v>1959</v>
-      </c>
-      <c r="G81" s="23"/>
-      <c r="H81" s="23"/>
+      <c r="C81" s="27" t="s">
+        <v>2019</v>
+      </c>
+      <c r="E81" s="24"/>
+      <c r="G81" s="22"/>
+      <c r="H81" s="22"/>
     </row>
     <row r="82" spans="1:8" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="19" t="s">
         <v>1960</v>
       </c>
-      <c r="B82" s="20" t="s">
+      <c r="B82" s="26" t="s">
         <v>1206</v>
       </c>
-      <c r="C82" s="24" t="s">
-        <v>2035</v>
-      </c>
-      <c r="E82" s="25" t="s">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C82" s="27" t="s">
+        <v>2018</v>
+      </c>
+      <c r="E82" s="24"/>
+    </row>
+    <row r="83" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="19" t="s">
         <v>1961</v>
       </c>
-      <c r="B83" s="20" t="s">
+      <c r="B83" s="26" t="s">
         <v>1632</v>
       </c>
-      <c r="C83" s="24" t="s">
-        <v>2034</v>
-      </c>
-      <c r="E83" s="25" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C83" s="27" t="s">
+        <v>2017</v>
+      </c>
+      <c r="E83" s="24"/>
+    </row>
+    <row r="84" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="19" t="s">
         <v>1962</v>
       </c>
-      <c r="B84" s="20" t="s">
+      <c r="B84" s="26" t="s">
         <v>1865</v>
       </c>
-      <c r="C84" s="24" t="s">
-        <v>2033</v>
-      </c>
-      <c r="E84" s="25" t="s">
-        <v>1962</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C84" s="27" t="s">
+        <v>2016</v>
+      </c>
+      <c r="E84" s="24"/>
+    </row>
+    <row r="85" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="19" t="s">
         <v>1963</v>
       </c>
-      <c r="B85" s="20" t="s">
+      <c r="B85" s="26" t="s">
         <v>1645</v>
       </c>
-      <c r="C85" s="24" t="s">
-        <v>2032</v>
-      </c>
-      <c r="E85" s="25" t="s">
-        <v>1963</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C85" s="27" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E85" s="24"/>
+    </row>
+    <row r="86" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="19" t="s">
         <v>1964</v>
       </c>
-      <c r="B86" s="20" t="s">
+      <c r="B86" s="26" t="s">
         <v>1077</v>
       </c>
-      <c r="C86" s="24" t="s">
-        <v>2031</v>
-      </c>
-      <c r="E86" s="25" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C86" s="27" t="s">
+        <v>2014</v>
+      </c>
+      <c r="E86" s="24"/>
+    </row>
+    <row r="87" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="19" t="s">
         <v>1965</v>
       </c>
-      <c r="B87" s="20" t="s">
+      <c r="B87" s="26" t="s">
         <v>1867</v>
       </c>
-      <c r="C87" s="24" t="s">
-        <v>2030</v>
-      </c>
-      <c r="E87" s="25" t="s">
-        <v>1965</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C87" s="27" t="s">
+        <v>2013</v>
+      </c>
+      <c r="E87" s="24"/>
+    </row>
+    <row r="88" spans="1:8" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="19" t="s">
         <v>1966</v>
       </c>
-      <c r="B88" s="20" t="s">
+      <c r="B88" s="26" t="s">
         <v>1644</v>
       </c>
-      <c r="C88" s="24" t="s">
-        <v>2029</v>
-      </c>
-      <c r="E88" s="25" t="s">
-        <v>1966</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C88" s="27" t="s">
+        <v>2012</v>
+      </c>
+      <c r="E88" s="24"/>
+    </row>
+    <row r="89" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="19" t="s">
         <v>1967</v>
       </c>
-      <c r="B89" s="20" t="s">
+      <c r="B89" s="26" t="s">
         <v>1064</v>
       </c>
-      <c r="C89" s="24" t="s">
-        <v>2028</v>
-      </c>
-      <c r="E89" s="25" t="s">
-        <v>1967</v>
-      </c>
+      <c r="C89" s="27" t="s">
+        <v>2011</v>
+      </c>
+      <c r="E89" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Proyecto Intermodular/Jira/Tablas Jira.xlsx
+++ b/Proyecto Intermodular/Jira/Tablas Jira.xlsx
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName name="Jira" localSheetId="1">Limpio!$A$1:$I$452</definedName>
     <definedName name="Jira" localSheetId="2">Ordenado!$A$1:$I$452</definedName>
-    <definedName name="Jira" localSheetId="5">Tabla1!$A$1:$I$452</definedName>
+    <definedName name="Jira" localSheetId="5">Tabla1!$B$1:$J$452</definedName>
     <definedName name="Jira" localSheetId="7">Tabla3!$B$1:$J$424</definedName>
     <definedName name="Jira" localSheetId="0">TODO!$A$1:$BC$452</definedName>
   </definedNames>
@@ -76160,1124 +76160,1124 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J89"/>
+  <dimension ref="B1:K89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.42578125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="69.5703125" customWidth="1"/>
-    <col min="6" max="6" width="56.42578125" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" customWidth="1"/>
-    <col min="8" max="8" width="82.7109375" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" customWidth="1"/>
-    <col min="10" max="10" width="97.140625" customWidth="1"/>
+    <col min="3" max="3" width="30.42578125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="69.5703125" customWidth="1"/>
+    <col min="7" max="7" width="56.42578125" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="82.7109375" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" customWidth="1"/>
+    <col min="11" max="11" width="97.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="20" t="s">
         <v>1878</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="C1" s="25" t="s">
         <v>1248</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="D1" s="21" t="s">
         <v>1879</v>
       </c>
-      <c r="E1" s="22"/>
       <c r="F1" s="22"/>
-    </row>
-    <row r="2" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="G1" s="22"/>
+    </row>
+    <row r="2" spans="2:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="19" t="s">
         <v>1880</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="C2" s="26" t="s">
         <v>1868</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="D2" s="27" t="s">
         <v>1969</v>
       </c>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
+      <c r="F2" s="24"/>
+    </row>
+    <row r="3" spans="2:7" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="19" t="s">
         <v>1881</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="C3" s="26" t="s">
         <v>1159</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="D3" s="27" t="s">
         <v>1968</v>
       </c>
-      <c r="E3" s="24"/>
-    </row>
-    <row r="4" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="F3" s="24"/>
+    </row>
+    <row r="4" spans="2:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="19" t="s">
         <v>1882</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="C4" s="26" t="s">
         <v>1168</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="D4" s="27" t="s">
         <v>1970</v>
       </c>
-      <c r="E4" s="24"/>
-    </row>
-    <row r="5" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+      <c r="F4" s="24"/>
+    </row>
+    <row r="5" spans="2:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="19" t="s">
         <v>1883</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="C5" s="26" t="s">
         <v>1171</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="D5" s="27" t="s">
         <v>1971</v>
       </c>
-      <c r="E5" s="24"/>
-    </row>
-    <row r="6" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
+      <c r="F5" s="24"/>
+    </row>
+    <row r="6" spans="2:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="19" t="s">
         <v>1884</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="C6" s="26" t="s">
         <v>1155</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="D6" s="27" t="s">
         <v>1972</v>
       </c>
-      <c r="E6" s="24"/>
-    </row>
-    <row r="7" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+      <c r="F6" s="24"/>
+    </row>
+    <row r="7" spans="2:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="19" t="s">
         <v>1885</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="C7" s="26" t="s">
         <v>1873</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="D7" s="27" t="s">
         <v>1973</v>
       </c>
-      <c r="E7" s="24"/>
-    </row>
-    <row r="8" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
+      <c r="F7" s="24"/>
+    </row>
+    <row r="8" spans="2:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="19" t="s">
         <v>1886</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="C8" s="26" t="s">
         <v>1671</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="D8" s="27" t="s">
         <v>1974</v>
       </c>
-      <c r="E8" s="24"/>
-    </row>
-    <row r="9" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
+      <c r="F8" s="24"/>
+    </row>
+    <row r="9" spans="2:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="19" t="s">
         <v>1887</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="C9" s="26" t="s">
         <v>1672</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="D9" s="27" t="s">
         <v>1975</v>
       </c>
-      <c r="E9" s="24"/>
-    </row>
-    <row r="10" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
+      <c r="F9" s="24"/>
+    </row>
+    <row r="10" spans="2:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="19" t="s">
         <v>1888</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="C10" s="26" t="s">
         <v>1670</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="D10" s="27" t="s">
         <v>1976</v>
       </c>
-      <c r="E10" s="24"/>
-    </row>
-    <row r="11" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+      <c r="F10" s="24"/>
+    </row>
+    <row r="11" spans="2:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="19" t="s">
         <v>1889</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="C11" s="26" t="s">
         <v>1794</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="D11" s="27" t="s">
         <v>1977</v>
       </c>
-      <c r="E11" s="24"/>
-    </row>
-    <row r="12" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
+      <c r="F11" s="24"/>
+    </row>
+    <row r="12" spans="2:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="19" t="s">
         <v>1890</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="C12" s="26" t="s">
         <v>1650</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="D12" s="27" t="s">
         <v>1978</v>
       </c>
-      <c r="E12" s="24"/>
-    </row>
-    <row r="13" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
+      <c r="F12" s="24"/>
+    </row>
+    <row r="13" spans="2:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="19" t="s">
         <v>1891</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="C13" s="26" t="s">
         <v>1103</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="D13" s="27" t="s">
         <v>1979</v>
       </c>
-      <c r="E13" s="24"/>
-    </row>
-    <row r="14" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
+      <c r="F13" s="24"/>
+    </row>
+    <row r="14" spans="2:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="19" t="s">
         <v>1892</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="C14" s="26" t="s">
         <v>1874</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="D14" s="27" t="s">
         <v>1980</v>
       </c>
-      <c r="E14" s="24"/>
-    </row>
-    <row r="15" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="19" t="s">
+      <c r="F14" s="24"/>
+    </row>
+    <row r="15" spans="2:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="19" t="s">
         <v>1893</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="C15" s="26" t="s">
         <v>1105</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="D15" s="27" t="s">
         <v>1981</v>
       </c>
-      <c r="E15" s="24"/>
-    </row>
-    <row r="16" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+      <c r="F15" s="24"/>
+    </row>
+    <row r="16" spans="2:7" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="19" t="s">
         <v>1894</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="C16" s="26" t="s">
         <v>1669</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="D16" s="27" t="s">
         <v>1982</v>
       </c>
-      <c r="E16" s="24"/>
-    </row>
-    <row r="17" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="19" t="s">
+      <c r="F16" s="24"/>
+    </row>
+    <row r="17" spans="2:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="19" t="s">
         <v>1895</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="C17" s="26" t="s">
         <v>1727</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="D17" s="27" t="s">
         <v>1983</v>
       </c>
-      <c r="E17" s="24"/>
-    </row>
-    <row r="18" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="19" t="s">
+      <c r="F17" s="24"/>
+    </row>
+    <row r="18" spans="2:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="19" t="s">
         <v>1896</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="C18" s="26" t="s">
         <v>1151</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="D18" s="27" t="s">
         <v>1984</v>
       </c>
-      <c r="E18" s="24"/>
-    </row>
-    <row r="19" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="19" t="s">
+      <c r="F18" s="24"/>
+    </row>
+    <row r="19" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="19" t="s">
         <v>1897</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="C19" s="26" t="s">
         <v>1726</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="D19" s="27" t="s">
         <v>1985</v>
       </c>
-      <c r="E19" s="24"/>
-    </row>
-    <row r="20" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="19" t="s">
+      <c r="F19" s="24"/>
+    </row>
+    <row r="20" spans="2:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="19" t="s">
         <v>1898</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="C20" s="26" t="s">
         <v>1148</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="D20" s="27" t="s">
         <v>1986</v>
       </c>
-      <c r="E20" s="24"/>
-    </row>
-    <row r="21" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="19" t="s">
+      <c r="F20" s="24"/>
+    </row>
+    <row r="21" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="19" t="s">
         <v>1899</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="C21" s="26" t="s">
         <v>1146</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="D21" s="27" t="s">
         <v>1987</v>
       </c>
-      <c r="E21" s="24"/>
-    </row>
-    <row r="22" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="19" t="s">
+      <c r="F21" s="24"/>
+    </row>
+    <row r="22" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="19" t="s">
         <v>1900</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="C22" s="26" t="s">
         <v>1665</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="D22" s="27" t="s">
         <v>1988</v>
       </c>
-      <c r="E22" s="24"/>
-    </row>
-    <row r="23" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="19" t="s">
+      <c r="F22" s="24"/>
+    </row>
+    <row r="23" spans="2:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="19" t="s">
         <v>1901</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="C23" s="26" t="s">
         <v>1660</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="D23" s="27" t="s">
         <v>1989</v>
       </c>
-      <c r="E23" s="24"/>
-    </row>
-    <row r="24" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="19" t="s">
+      <c r="F23" s="24"/>
+    </row>
+    <row r="24" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="19" t="s">
         <v>1902</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="C24" s="26" t="s">
         <v>1132</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="D24" s="27" t="s">
         <v>1990</v>
       </c>
-      <c r="E24" s="24"/>
-    </row>
-    <row r="25" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="19" t="s">
+      <c r="F24" s="24"/>
+    </row>
+    <row r="25" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="19" t="s">
         <v>1903</v>
       </c>
-      <c r="B25" s="26" t="s">
+      <c r="C25" s="26" t="s">
         <v>1659</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="D25" s="27" t="s">
         <v>1991</v>
       </c>
-      <c r="E25" s="24"/>
-    </row>
-    <row r="26" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="19" t="s">
+      <c r="F25" s="24"/>
+    </row>
+    <row r="26" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="19" t="s">
         <v>1904</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="C26" s="26" t="s">
         <v>1658</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="D26" s="27" t="s">
         <v>1992</v>
       </c>
-      <c r="E26" s="24"/>
-    </row>
-    <row r="27" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="19" t="s">
+      <c r="F26" s="24"/>
+    </row>
+    <row r="27" spans="2:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="19" t="s">
         <v>1905</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="C27" s="26" t="s">
         <v>1126</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="D27" s="27" t="s">
         <v>1993</v>
       </c>
-      <c r="E27" s="24"/>
-    </row>
-    <row r="28" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="19" t="s">
+      <c r="F27" s="24"/>
+    </row>
+    <row r="28" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="19" t="s">
         <v>1906</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="C28" s="26" t="s">
         <v>1657</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="D28" s="27" t="s">
         <v>1994</v>
       </c>
-      <c r="E28" s="24"/>
-    </row>
-    <row r="29" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="19" t="s">
+      <c r="F28" s="24"/>
+    </row>
+    <row r="29" spans="2:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="19" t="s">
         <v>1907</v>
       </c>
-      <c r="B29" s="26" t="s">
+      <c r="C29" s="26" t="s">
         <v>1228</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="D29" s="27" t="s">
         <v>1995</v>
       </c>
-      <c r="E29" s="24"/>
-    </row>
-    <row r="30" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="19" t="s">
+      <c r="F29" s="24"/>
+    </row>
+    <row r="30" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="19" t="s">
         <v>1908</v>
       </c>
-      <c r="B30" s="26" t="s">
+      <c r="C30" s="26" t="s">
         <v>1872</v>
       </c>
-      <c r="C30" s="27" t="s">
+      <c r="D30" s="27" t="s">
         <v>1996</v>
       </c>
-      <c r="E30" s="24"/>
-    </row>
-    <row r="31" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="19" t="s">
+      <c r="F30" s="24"/>
+    </row>
+    <row r="31" spans="2:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="19" t="s">
         <v>1909</v>
       </c>
-      <c r="B31" s="26" t="s">
+      <c r="C31" s="26" t="s">
         <v>1663</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="D31" s="27" t="s">
         <v>1997</v>
       </c>
-      <c r="E31" s="24"/>
-    </row>
-    <row r="32" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="19" t="s">
+      <c r="F31" s="24"/>
+    </row>
+    <row r="32" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="19" t="s">
         <v>1910</v>
       </c>
-      <c r="B32" s="26" t="s">
+      <c r="C32" s="26" t="s">
         <v>1229</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="D32" s="27" t="s">
         <v>1998</v>
       </c>
-      <c r="E32" s="24"/>
-    </row>
-    <row r="33" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="19" t="s">
+      <c r="F32" s="24"/>
+    </row>
+    <row r="33" spans="2:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="19" t="s">
         <v>1911</v>
       </c>
-      <c r="B33" s="26" t="s">
+      <c r="C33" s="26" t="s">
         <v>1655</v>
       </c>
-      <c r="C33" s="27" t="s">
+      <c r="D33" s="27" t="s">
         <v>1999</v>
       </c>
-      <c r="E33" s="24"/>
-    </row>
-    <row r="34" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="19" t="s">
+      <c r="F33" s="24"/>
+    </row>
+    <row r="34" spans="2:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="19" t="s">
         <v>1912</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="C34" s="26" t="s">
         <v>1656</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="D34" s="27" t="s">
         <v>2000</v>
       </c>
-      <c r="E34" s="24"/>
-    </row>
-    <row r="35" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="19" t="s">
+      <c r="F34" s="24"/>
+    </row>
+    <row r="35" spans="2:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="19" t="s">
         <v>1913</v>
       </c>
-      <c r="B35" s="26" t="s">
+      <c r="C35" s="26" t="s">
         <v>1117</v>
       </c>
-      <c r="C35" s="27" t="s">
+      <c r="D35" s="27" t="s">
         <v>2001</v>
       </c>
-      <c r="E35" s="24"/>
-    </row>
-    <row r="36" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="19" t="s">
+      <c r="F35" s="24"/>
+    </row>
+    <row r="36" spans="2:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="19" t="s">
         <v>1914</v>
       </c>
-      <c r="B36" s="26" t="s">
+      <c r="C36" s="26" t="s">
         <v>1870</v>
       </c>
-      <c r="C36" s="27" t="s">
+      <c r="D36" s="27" t="s">
         <v>2002</v>
       </c>
-      <c r="E36" s="24"/>
-    </row>
-    <row r="37" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="19" t="s">
+      <c r="F36" s="24"/>
+    </row>
+    <row r="37" spans="2:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="19" t="s">
         <v>1915</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="C37" s="26" t="s">
         <v>1871</v>
       </c>
-      <c r="C37" s="27" t="s">
+      <c r="D37" s="27" t="s">
         <v>2003</v>
       </c>
-      <c r="E37" s="24"/>
-    </row>
-    <row r="38" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="19" t="s">
+      <c r="F37" s="24"/>
+    </row>
+    <row r="38" spans="2:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="19" t="s">
         <v>1916</v>
       </c>
-      <c r="B38" s="26" t="s">
+      <c r="C38" s="26" t="s">
         <v>1792</v>
       </c>
-      <c r="C38" s="27" t="s">
+      <c r="D38" s="27" t="s">
         <v>2004</v>
       </c>
-      <c r="E38" s="24"/>
-    </row>
-    <row r="39" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="19" t="s">
+      <c r="F38" s="24"/>
+    </row>
+    <row r="39" spans="2:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="19" t="s">
         <v>1917</v>
       </c>
-      <c r="B39" s="26" t="s">
+      <c r="C39" s="26" t="s">
         <v>1637</v>
       </c>
-      <c r="C39" s="27" t="s">
+      <c r="D39" s="27" t="s">
         <v>2005</v>
       </c>
-      <c r="E39" s="24"/>
-    </row>
-    <row r="40" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="19" t="s">
+      <c r="F39" s="24"/>
+    </row>
+    <row r="40" spans="2:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="19" t="s">
         <v>1918</v>
       </c>
-      <c r="B40" s="26" t="s">
+      <c r="C40" s="26" t="s">
         <v>1661</v>
       </c>
-      <c r="C40" s="27" t="s">
+      <c r="D40" s="27" t="s">
         <v>2006</v>
       </c>
-      <c r="E40" s="24"/>
-    </row>
-    <row r="41" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="19" t="s">
+      <c r="F40" s="24"/>
+    </row>
+    <row r="41" spans="2:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="19" t="s">
         <v>1919</v>
       </c>
-      <c r="B41" s="26" t="s">
+      <c r="C41" s="26" t="s">
         <v>1795</v>
       </c>
-      <c r="C41" s="27" t="s">
+      <c r="D41" s="27" t="s">
         <v>2007</v>
       </c>
-      <c r="E41" s="24"/>
-    </row>
-    <row r="42" spans="1:10" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="19" t="s">
+      <c r="F41" s="24"/>
+    </row>
+    <row r="42" spans="2:11" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="19" t="s">
         <v>1920</v>
       </c>
-      <c r="B42" s="26" t="s">
+      <c r="C42" s="26" t="s">
         <v>1244</v>
       </c>
-      <c r="C42" s="27" t="s">
+      <c r="D42" s="27" t="s">
         <v>2008</v>
       </c>
-      <c r="E42" s="24"/>
-    </row>
-    <row r="43" spans="1:10" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="19" t="s">
+      <c r="F42" s="24"/>
+    </row>
+    <row r="43" spans="2:11" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="19" t="s">
         <v>1921</v>
       </c>
-      <c r="B43" s="26" t="s">
+      <c r="C43" s="26" t="s">
         <v>1869</v>
       </c>
-      <c r="C43" s="27" t="s">
+      <c r="D43" s="27" t="s">
         <v>2009</v>
       </c>
-      <c r="E43" s="24"/>
-    </row>
-    <row r="44" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="19" t="s">
+      <c r="F43" s="24"/>
+    </row>
+    <row r="44" spans="2:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="19" t="s">
         <v>1922</v>
       </c>
-      <c r="B44" s="26" t="s">
+      <c r="C44" s="26" t="s">
         <v>1662</v>
       </c>
-      <c r="C44" s="27" t="s">
+      <c r="D44" s="27" t="s">
         <v>2010</v>
       </c>
-      <c r="E44" s="24"/>
-      <c r="G44" s="22"/>
+      <c r="F44" s="24"/>
       <c r="H44" s="22"/>
-    </row>
-    <row r="45" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="19" t="s">
+      <c r="I44" s="22"/>
+    </row>
+    <row r="45" spans="2:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="19" t="s">
         <v>1923</v>
       </c>
-      <c r="B45" s="26" t="s">
+      <c r="C45" s="26" t="s">
         <v>1203</v>
       </c>
-      <c r="C45" s="27" t="s">
+      <c r="D45" s="27" t="s">
         <v>2039</v>
       </c>
-      <c r="E45" s="24"/>
-      <c r="I45" s="24"/>
-      <c r="J45" s="23"/>
-    </row>
-    <row r="46" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="19" t="s">
+      <c r="F45" s="24"/>
+      <c r="J45" s="24"/>
+      <c r="K45" s="23"/>
+    </row>
+    <row r="46" spans="2:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="19" t="s">
         <v>1924</v>
       </c>
-      <c r="B46" s="26" t="s">
+      <c r="C46" s="26" t="s">
         <v>1201</v>
       </c>
-      <c r="C46" s="27" t="s">
+      <c r="D46" s="27" t="s">
         <v>2040</v>
       </c>
-      <c r="E46" s="24"/>
-      <c r="I46" s="24"/>
-      <c r="J46" s="23"/>
-    </row>
-    <row r="47" spans="1:10" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="19" t="s">
+      <c r="F46" s="24"/>
+      <c r="J46" s="24"/>
+      <c r="K46" s="23"/>
+    </row>
+    <row r="47" spans="2:11" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="19" t="s">
         <v>1925</v>
       </c>
-      <c r="B47" s="26" t="s">
+      <c r="C47" s="26" t="s">
         <v>1202</v>
       </c>
-      <c r="C47" s="27" t="s">
+      <c r="D47" s="27" t="s">
         <v>2041</v>
       </c>
-      <c r="E47" s="24"/>
-      <c r="I47" s="24"/>
-      <c r="J47" s="23"/>
-    </row>
-    <row r="48" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="19" t="s">
+      <c r="F47" s="24"/>
+      <c r="J47" s="24"/>
+      <c r="K47" s="23"/>
+    </row>
+    <row r="48" spans="2:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="19" t="s">
         <v>1926</v>
       </c>
-      <c r="B48" s="26" t="s">
+      <c r="C48" s="26" t="s">
         <v>1652</v>
       </c>
-      <c r="C48" s="27" t="s">
+      <c r="D48" s="27" t="s">
         <v>2042</v>
       </c>
-      <c r="E48" s="24"/>
-      <c r="I48" s="24"/>
-      <c r="J48" s="23"/>
-    </row>
-    <row r="49" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="19" t="s">
+      <c r="F48" s="24"/>
+      <c r="J48" s="24"/>
+      <c r="K48" s="23"/>
+    </row>
+    <row r="49" spans="2:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="19" t="s">
         <v>1927</v>
       </c>
-      <c r="B49" s="26" t="s">
+      <c r="C49" s="26" t="s">
         <v>1654</v>
       </c>
-      <c r="C49" s="27" t="s">
+      <c r="D49" s="27" t="s">
         <v>2043</v>
       </c>
-      <c r="E49" s="24"/>
-      <c r="I49" s="24"/>
-      <c r="J49" s="23"/>
-    </row>
-    <row r="50" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="19" t="s">
+      <c r="F49" s="24"/>
+      <c r="J49" s="24"/>
+      <c r="K49" s="23"/>
+    </row>
+    <row r="50" spans="2:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="19" t="s">
         <v>1928</v>
       </c>
-      <c r="B50" s="26" t="s">
+      <c r="C50" s="26" t="s">
         <v>1648</v>
       </c>
-      <c r="C50" s="27" t="s">
+      <c r="D50" s="27" t="s">
         <v>2044</v>
       </c>
-      <c r="E50" s="24"/>
-      <c r="I50" s="24"/>
-      <c r="J50" s="23"/>
-    </row>
-    <row r="51" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="19" t="s">
+      <c r="F50" s="24"/>
+      <c r="J50" s="24"/>
+      <c r="K50" s="23"/>
+    </row>
+    <row r="51" spans="2:11" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="19" t="s">
         <v>1929</v>
       </c>
-      <c r="B51" s="26" t="s">
+      <c r="C51" s="26" t="s">
         <v>1647</v>
       </c>
-      <c r="C51" s="27" t="s">
+      <c r="D51" s="27" t="s">
         <v>2045</v>
       </c>
-      <c r="E51" s="24"/>
-      <c r="I51" s="24"/>
-      <c r="J51" s="23"/>
-    </row>
-    <row r="52" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="19" t="s">
+      <c r="F51" s="24"/>
+      <c r="J51" s="24"/>
+      <c r="K51" s="23"/>
+    </row>
+    <row r="52" spans="2:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="19" t="s">
         <v>1930</v>
       </c>
-      <c r="B52" s="26" t="s">
+      <c r="C52" s="26" t="s">
         <v>1092</v>
       </c>
-      <c r="C52" s="27" t="s">
+      <c r="D52" s="27" t="s">
         <v>2046</v>
       </c>
-      <c r="E52" s="24"/>
-      <c r="I52" s="24"/>
-      <c r="J52" s="23"/>
-    </row>
-    <row r="53" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="19" t="s">
+      <c r="F52" s="24"/>
+      <c r="J52" s="24"/>
+      <c r="K52" s="23"/>
+    </row>
+    <row r="53" spans="2:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="19" t="s">
         <v>1931</v>
       </c>
-      <c r="B53" s="26" t="s">
+      <c r="C53" s="26" t="s">
         <v>1094</v>
       </c>
-      <c r="C53" s="27" t="s">
+      <c r="D53" s="27" t="s">
         <v>2047</v>
       </c>
-      <c r="E53" s="24"/>
-      <c r="I53" s="24"/>
-      <c r="J53" s="23"/>
-    </row>
-    <row r="54" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="19" t="s">
+      <c r="F53" s="24"/>
+      <c r="J53" s="24"/>
+      <c r="K53" s="23"/>
+    </row>
+    <row r="54" spans="2:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="19" t="s">
         <v>1932</v>
       </c>
-      <c r="B54" s="26" t="s">
+      <c r="C54" s="26" t="s">
         <v>1096</v>
       </c>
-      <c r="C54" s="27" t="s">
+      <c r="D54" s="27" t="s">
         <v>2048</v>
       </c>
-      <c r="E54" s="24"/>
-      <c r="I54" s="24"/>
-      <c r="J54" s="23"/>
-    </row>
-    <row r="55" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="19" t="s">
+      <c r="F54" s="24"/>
+      <c r="J54" s="24"/>
+      <c r="K54" s="23"/>
+    </row>
+    <row r="55" spans="2:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="19" t="s">
         <v>1933</v>
       </c>
-      <c r="B55" s="26" t="s">
+      <c r="C55" s="26" t="s">
         <v>1098</v>
       </c>
-      <c r="C55" s="27" t="s">
+      <c r="D55" s="27" t="s">
         <v>2049</v>
       </c>
-      <c r="E55" s="24"/>
-      <c r="I55" s="24"/>
-      <c r="J55" s="23"/>
-    </row>
-    <row r="56" spans="1:10" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="19" t="s">
+      <c r="F55" s="24"/>
+      <c r="J55" s="24"/>
+      <c r="K55" s="23"/>
+    </row>
+    <row r="56" spans="2:11" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="19" t="s">
         <v>1934</v>
       </c>
-      <c r="B56" s="26" t="s">
+      <c r="C56" s="26" t="s">
         <v>1090</v>
       </c>
-      <c r="C56" s="27" t="s">
+      <c r="D56" s="27" t="s">
         <v>2050</v>
       </c>
-      <c r="E56" s="24"/>
-      <c r="I56" s="24"/>
-      <c r="J56" s="23"/>
-    </row>
-    <row r="57" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="19" t="s">
+      <c r="F56" s="24"/>
+      <c r="J56" s="24"/>
+      <c r="K56" s="23"/>
+    </row>
+    <row r="57" spans="2:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="19" t="s">
         <v>1935</v>
       </c>
-      <c r="B57" s="26" t="s">
+      <c r="C57" s="26" t="s">
         <v>1861</v>
       </c>
-      <c r="C57" s="27" t="s">
+      <c r="D57" s="27" t="s">
         <v>2051</v>
       </c>
-      <c r="E57" s="24"/>
-      <c r="I57" s="24"/>
-      <c r="J57" s="23"/>
-    </row>
-    <row r="58" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="19" t="s">
+      <c r="F57" s="24"/>
+      <c r="J57" s="24"/>
+      <c r="K57" s="23"/>
+    </row>
+    <row r="58" spans="2:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="19" t="s">
         <v>1936</v>
       </c>
-      <c r="B58" s="26" t="s">
+      <c r="C58" s="26" t="s">
         <v>1787</v>
       </c>
-      <c r="C58" s="27" t="s">
+      <c r="D58" s="27" t="s">
         <v>2052</v>
       </c>
-      <c r="E58" s="24"/>
-      <c r="I58" s="24"/>
-      <c r="J58" s="23"/>
-    </row>
-    <row r="59" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="19" t="s">
+      <c r="F58" s="24"/>
+      <c r="J58" s="24"/>
+      <c r="K58" s="23"/>
+    </row>
+    <row r="59" spans="2:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="19" t="s">
         <v>1937</v>
       </c>
-      <c r="B59" s="26" t="s">
+      <c r="C59" s="26" t="s">
         <v>1624</v>
       </c>
-      <c r="C59" s="27" t="s">
+      <c r="D59" s="27" t="s">
         <v>2053</v>
       </c>
-      <c r="E59" s="24"/>
-      <c r="I59" s="24"/>
-      <c r="J59" s="23"/>
-    </row>
-    <row r="60" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="19" t="s">
+      <c r="F59" s="24"/>
+      <c r="J59" s="24"/>
+      <c r="K59" s="23"/>
+    </row>
+    <row r="60" spans="2:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="19" t="s">
         <v>1938</v>
       </c>
-      <c r="B60" s="26" t="s">
+      <c r="C60" s="26" t="s">
         <v>1211</v>
       </c>
-      <c r="C60" s="27" t="s">
+      <c r="D60" s="27" t="s">
         <v>2054</v>
       </c>
-      <c r="E60" s="24"/>
-      <c r="I60" s="24"/>
-      <c r="J60" s="23"/>
-    </row>
-    <row r="61" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="19" t="s">
+      <c r="F60" s="24"/>
+      <c r="J60" s="24"/>
+      <c r="K60" s="23"/>
+    </row>
+    <row r="61" spans="2:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="19" t="s">
         <v>1939</v>
       </c>
-      <c r="B61" s="26" t="s">
+      <c r="C61" s="26" t="s">
         <v>1209</v>
       </c>
-      <c r="C61" s="27" t="s">
+      <c r="D61" s="27" t="s">
         <v>2055</v>
       </c>
-      <c r="E61" s="24"/>
-      <c r="I61" s="24"/>
-      <c r="J61" s="23"/>
-    </row>
-    <row r="62" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="19" t="s">
+      <c r="F61" s="24"/>
+      <c r="J61" s="24"/>
+      <c r="K61" s="23"/>
+    </row>
+    <row r="62" spans="2:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="19" t="s">
         <v>1940</v>
       </c>
-      <c r="B62" s="26" t="s">
+      <c r="C62" s="26" t="s">
         <v>1210</v>
       </c>
-      <c r="C62" s="27" t="s">
+      <c r="D62" s="27" t="s">
         <v>2038</v>
       </c>
-      <c r="E62" s="24"/>
-    </row>
-    <row r="63" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="19" t="s">
+      <c r="F62" s="24"/>
+    </row>
+    <row r="63" spans="2:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="19" t="s">
         <v>1941</v>
       </c>
-      <c r="B63" s="26" t="s">
+      <c r="C63" s="26" t="s">
         <v>1208</v>
       </c>
-      <c r="C63" s="27" t="s">
+      <c r="D63" s="27" t="s">
         <v>2037</v>
       </c>
-      <c r="E63" s="24"/>
-    </row>
-    <row r="64" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="19" t="s">
+      <c r="F63" s="24"/>
+    </row>
+    <row r="64" spans="2:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="19" t="s">
         <v>1942</v>
       </c>
-      <c r="B64" s="26" t="s">
+      <c r="C64" s="26" t="s">
         <v>1642</v>
       </c>
-      <c r="C64" s="27" t="s">
+      <c r="D64" s="27" t="s">
         <v>2036</v>
       </c>
-      <c r="E64" s="24"/>
-    </row>
-    <row r="65" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="19" t="s">
+      <c r="F64" s="24"/>
+    </row>
+    <row r="65" spans="2:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="19" t="s">
         <v>1943</v>
       </c>
-      <c r="B65" s="26" t="s">
+      <c r="C65" s="26" t="s">
         <v>1643</v>
       </c>
-      <c r="C65" s="27" t="s">
+      <c r="D65" s="27" t="s">
         <v>2035</v>
       </c>
-      <c r="E65" s="24"/>
-    </row>
-    <row r="66" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="19" t="s">
+      <c r="F65" s="24"/>
+    </row>
+    <row r="66" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="19" t="s">
         <v>1944</v>
       </c>
-      <c r="B66" s="26" t="s">
+      <c r="C66" s="26" t="s">
         <v>1646</v>
       </c>
-      <c r="C66" s="27" t="s">
+      <c r="D66" s="27" t="s">
         <v>2034</v>
       </c>
-      <c r="E66" s="24"/>
-    </row>
-    <row r="67" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="19" t="s">
+      <c r="F66" s="24"/>
+    </row>
+    <row r="67" spans="2:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="19" t="s">
         <v>1945</v>
       </c>
-      <c r="B67" s="26" t="s">
+      <c r="C67" s="26" t="s">
         <v>1080</v>
       </c>
-      <c r="C67" s="27" t="s">
+      <c r="D67" s="27" t="s">
         <v>2033</v>
       </c>
-      <c r="E67" s="24"/>
-    </row>
-    <row r="68" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="19" t="s">
+      <c r="F67" s="24"/>
+    </row>
+    <row r="68" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="19" t="s">
         <v>1946</v>
       </c>
-      <c r="B68" s="26" t="s">
+      <c r="C68" s="26" t="s">
         <v>1073</v>
       </c>
-      <c r="C68" s="27" t="s">
+      <c r="D68" s="27" t="s">
         <v>2032</v>
       </c>
-      <c r="E68" s="24"/>
-    </row>
-    <row r="69" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="19" t="s">
+      <c r="F68" s="24"/>
+    </row>
+    <row r="69" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="19" t="s">
         <v>1947</v>
       </c>
-      <c r="B69" s="26" t="s">
+      <c r="C69" s="26" t="s">
         <v>1866</v>
       </c>
-      <c r="C69" s="27" t="s">
+      <c r="D69" s="27" t="s">
         <v>2031</v>
       </c>
-      <c r="E69" s="24"/>
-    </row>
-    <row r="70" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="19" t="s">
+      <c r="F69" s="24"/>
+    </row>
+    <row r="70" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="19" t="s">
         <v>1948</v>
       </c>
-      <c r="B70" s="26" t="s">
+      <c r="C70" s="26" t="s">
         <v>1724</v>
       </c>
-      <c r="C70" s="27" t="s">
+      <c r="D70" s="27" t="s">
         <v>2030</v>
       </c>
-      <c r="E70" s="24"/>
-    </row>
-    <row r="71" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="19" t="s">
+      <c r="F70" s="24"/>
+    </row>
+    <row r="71" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="19" t="s">
         <v>1949</v>
       </c>
-      <c r="B71" s="26" t="s">
+      <c r="C71" s="26" t="s">
         <v>1723</v>
       </c>
-      <c r="C71" s="27" t="s">
+      <c r="D71" s="27" t="s">
         <v>2029</v>
       </c>
-      <c r="E71" s="24"/>
-    </row>
-    <row r="72" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="19" t="s">
+      <c r="F71" s="24"/>
+    </row>
+    <row r="72" spans="2:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="19" t="s">
         <v>1950</v>
       </c>
-      <c r="B72" s="26" t="s">
+      <c r="C72" s="26" t="s">
         <v>1635</v>
       </c>
-      <c r="C72" s="27" t="s">
+      <c r="D72" s="27" t="s">
         <v>2028</v>
       </c>
-      <c r="E72" s="24"/>
-    </row>
-    <row r="73" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="19" t="s">
+      <c r="F72" s="24"/>
+    </row>
+    <row r="73" spans="2:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="19" t="s">
         <v>1951</v>
       </c>
-      <c r="B73" s="26" t="s">
+      <c r="C73" s="26" t="s">
         <v>1633</v>
       </c>
-      <c r="C73" s="27" t="s">
+      <c r="D73" s="27" t="s">
         <v>2027</v>
       </c>
-      <c r="E73" s="24"/>
-    </row>
-    <row r="74" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="19" t="s">
+      <c r="F73" s="24"/>
+    </row>
+    <row r="74" spans="2:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="19" t="s">
         <v>1952</v>
       </c>
-      <c r="B74" s="26" t="s">
+      <c r="C74" s="26" t="s">
         <v>1793</v>
       </c>
-      <c r="C74" s="27" t="s">
+      <c r="D74" s="27" t="s">
         <v>2026</v>
       </c>
-      <c r="E74" s="24"/>
-    </row>
-    <row r="75" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="19" t="s">
+      <c r="F74" s="24"/>
+    </row>
+    <row r="75" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="19" t="s">
         <v>1953</v>
       </c>
-      <c r="B75" s="26" t="s">
+      <c r="C75" s="26" t="s">
         <v>1058</v>
       </c>
-      <c r="C75" s="27" t="s">
+      <c r="D75" s="27" t="s">
         <v>2025</v>
       </c>
-      <c r="E75" s="24"/>
-    </row>
-    <row r="76" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="19" t="s">
+      <c r="F75" s="24"/>
+    </row>
+    <row r="76" spans="2:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="19" t="s">
         <v>1954</v>
       </c>
-      <c r="B76" s="26" t="s">
+      <c r="C76" s="26" t="s">
         <v>1639</v>
       </c>
-      <c r="C76" s="27" t="s">
+      <c r="D76" s="27" t="s">
         <v>2024</v>
       </c>
-      <c r="E76" s="24"/>
-    </row>
-    <row r="77" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="19" t="s">
+      <c r="F76" s="24"/>
+    </row>
+    <row r="77" spans="2:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="19" t="s">
         <v>1955</v>
       </c>
-      <c r="B77" s="26" t="s">
+      <c r="C77" s="26" t="s">
         <v>1640</v>
       </c>
-      <c r="C77" s="27" t="s">
+      <c r="D77" s="27" t="s">
         <v>2023</v>
       </c>
-      <c r="E77" s="24"/>
-    </row>
-    <row r="78" spans="1:5" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="19" t="s">
+      <c r="F77" s="24"/>
+    </row>
+    <row r="78" spans="2:6" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="19" t="s">
         <v>1956</v>
       </c>
-      <c r="B78" s="26" t="s">
+      <c r="C78" s="26" t="s">
         <v>1641</v>
       </c>
-      <c r="C78" s="27" t="s">
+      <c r="D78" s="27" t="s">
         <v>2022</v>
       </c>
-      <c r="E78" s="24"/>
-    </row>
-    <row r="79" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="19" t="s">
+      <c r="F78" s="24"/>
+    </row>
+    <row r="79" spans="2:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="19" t="s">
         <v>1957</v>
       </c>
-      <c r="B79" s="26" t="s">
+      <c r="C79" s="26" t="s">
         <v>1207</v>
       </c>
-      <c r="C79" s="27" t="s">
+      <c r="D79" s="27" t="s">
         <v>2021</v>
       </c>
-      <c r="E79" s="24"/>
-    </row>
-    <row r="80" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="19" t="s">
+      <c r="F79" s="24"/>
+    </row>
+    <row r="80" spans="2:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="19" t="s">
         <v>1958</v>
       </c>
-      <c r="B80" s="26" t="s">
+      <c r="C80" s="26" t="s">
         <v>1204</v>
       </c>
-      <c r="C80" s="27" t="s">
+      <c r="D80" s="27" t="s">
         <v>2020</v>
       </c>
-      <c r="E80" s="24"/>
-    </row>
-    <row r="81" spans="1:8" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="19" t="s">
+      <c r="F80" s="24"/>
+    </row>
+    <row r="81" spans="2:9" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="19" t="s">
         <v>1959</v>
       </c>
-      <c r="B81" s="26" t="s">
+      <c r="C81" s="26" t="s">
         <v>1205</v>
       </c>
-      <c r="C81" s="27" t="s">
+      <c r="D81" s="27" t="s">
         <v>2019</v>
       </c>
-      <c r="E81" s="24"/>
-      <c r="G81" s="22"/>
+      <c r="F81" s="24"/>
       <c r="H81" s="22"/>
-    </row>
-    <row r="82" spans="1:8" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="19" t="s">
+      <c r="I81" s="22"/>
+    </row>
+    <row r="82" spans="2:9" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="19" t="s">
         <v>1960</v>
       </c>
-      <c r="B82" s="26" t="s">
+      <c r="C82" s="26" t="s">
         <v>1206</v>
       </c>
-      <c r="C82" s="27" t="s">
+      <c r="D82" s="27" t="s">
         <v>2018</v>
       </c>
-      <c r="E82" s="24"/>
-    </row>
-    <row r="83" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="19" t="s">
+      <c r="F82" s="24"/>
+    </row>
+    <row r="83" spans="2:9" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="19" t="s">
         <v>1961</v>
       </c>
-      <c r="B83" s="26" t="s">
+      <c r="C83" s="26" t="s">
         <v>1632</v>
       </c>
-      <c r="C83" s="27" t="s">
+      <c r="D83" s="27" t="s">
         <v>2017</v>
       </c>
-      <c r="E83" s="24"/>
-    </row>
-    <row r="84" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="19" t="s">
+      <c r="F83" s="24"/>
+    </row>
+    <row r="84" spans="2:9" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="19" t="s">
         <v>1962</v>
       </c>
-      <c r="B84" s="26" t="s">
+      <c r="C84" s="26" t="s">
         <v>1865</v>
       </c>
-      <c r="C84" s="27" t="s">
+      <c r="D84" s="27" t="s">
         <v>2016</v>
       </c>
-      <c r="E84" s="24"/>
-    </row>
-    <row r="85" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="19" t="s">
+      <c r="F84" s="24"/>
+    </row>
+    <row r="85" spans="2:9" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B85" s="19" t="s">
         <v>1963</v>
       </c>
-      <c r="B85" s="26" t="s">
+      <c r="C85" s="26" t="s">
         <v>1645</v>
       </c>
-      <c r="C85" s="27" t="s">
+      <c r="D85" s="27" t="s">
         <v>2015</v>
       </c>
-      <c r="E85" s="24"/>
-    </row>
-    <row r="86" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="19" t="s">
+      <c r="F85" s="24"/>
+    </row>
+    <row r="86" spans="2:9" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B86" s="19" t="s">
         <v>1964</v>
       </c>
-      <c r="B86" s="26" t="s">
+      <c r="C86" s="26" t="s">
         <v>1077</v>
       </c>
-      <c r="C86" s="27" t="s">
+      <c r="D86" s="27" t="s">
         <v>2014</v>
       </c>
-      <c r="E86" s="24"/>
-    </row>
-    <row r="87" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="19" t="s">
+      <c r="F86" s="24"/>
+    </row>
+    <row r="87" spans="2:9" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B87" s="19" t="s">
         <v>1965</v>
       </c>
-      <c r="B87" s="26" t="s">
+      <c r="C87" s="26" t="s">
         <v>1867</v>
       </c>
-      <c r="C87" s="27" t="s">
+      <c r="D87" s="27" t="s">
         <v>2013</v>
       </c>
-      <c r="E87" s="24"/>
-    </row>
-    <row r="88" spans="1:8" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="19" t="s">
+      <c r="F87" s="24"/>
+    </row>
+    <row r="88" spans="2:9" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B88" s="19" t="s">
         <v>1966</v>
       </c>
-      <c r="B88" s="26" t="s">
+      <c r="C88" s="26" t="s">
         <v>1644</v>
       </c>
-      <c r="C88" s="27" t="s">
+      <c r="D88" s="27" t="s">
         <v>2012</v>
       </c>
-      <c r="E88" s="24"/>
-    </row>
-    <row r="89" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="19" t="s">
+      <c r="F88" s="24"/>
+    </row>
+    <row r="89" spans="2:9" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="19" t="s">
         <v>1967</v>
       </c>
-      <c r="B89" s="26" t="s">
+      <c r="C89" s="26" t="s">
         <v>1064</v>
       </c>
-      <c r="C89" s="27" t="s">
+      <c r="D89" s="27" t="s">
         <v>2011</v>
       </c>
-      <c r="E89" s="24"/>
+      <c r="F89" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Proyecto Intermodular/Jira/Tablas Jira.xlsx
+++ b/Proyecto Intermodular/Jira/Tablas Jira.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="29040" windowHeight="16440" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="29040" windowHeight="16440" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="TODO" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
     <sheet name="Sprints" sheetId="3" r:id="rId4"/>
     <sheet name="Caracteres" sheetId="6" r:id="rId5"/>
     <sheet name="Tabla1" sheetId="9" r:id="rId6"/>
-    <sheet name="Tabla2" sheetId="7" r:id="rId7"/>
-    <sheet name="Tabla3" sheetId="8" r:id="rId8"/>
+    <sheet name="Tabla2" sheetId="8" r:id="rId7"/>
+    <sheet name="Tabla3" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="Jira" localSheetId="1">Limpio!$A$1:$I$452</definedName>
     <definedName name="Jira" localSheetId="2">Ordenado!$A$1:$I$452</definedName>
     <definedName name="Jira" localSheetId="5">Tabla1!$B$1:$J$452</definedName>
-    <definedName name="Jira" localSheetId="7">Tabla3!$B$1:$J$424</definedName>
+    <definedName name="Jira" localSheetId="6">Tabla2!$B$1:$J$424</definedName>
     <definedName name="Jira" localSheetId="0">TODO!$A$1:$BC$452</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -348,7 +348,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20738" uniqueCount="2056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20760" uniqueCount="2076">
   <si>
     <t>Resumen</t>
   </si>
@@ -6788,6 +6788,66 @@
  - Los resultados se actualizan según el filtro aplicado.
  - La búsqueda funciona según los criterios disponibles.
  - Si ocurre error, se muestra aviso.</t>
+  </si>
+  <si>
+    <t>Tarea</t>
+  </si>
+  <si>
+    <t>Fecha Inicio</t>
+  </si>
+  <si>
+    <t>Documento Acuerdo de Proyecto</t>
+  </si>
+  <si>
+    <t>Diseño estructura BBDD</t>
+  </si>
+  <si>
+    <t>Diseño interfaz Mockup</t>
+  </si>
+  <si>
+    <t>Documento Análisis</t>
+  </si>
+  <si>
+    <t>Sprint 1 Semana 1</t>
+  </si>
+  <si>
+    <t>Sprint 2 Semana 2</t>
+  </si>
+  <si>
+    <t>Sprint 3 Semana 3</t>
+  </si>
+  <si>
+    <t>Sprint 4 Semana 4</t>
+  </si>
+  <si>
+    <t>Sprint 5 Semana 5</t>
+  </si>
+  <si>
+    <t>Sprint 6 Semana 6</t>
+  </si>
+  <si>
+    <t>Sprint 7 Semana 7</t>
+  </si>
+  <si>
+    <t>Sprint 8 Semana 8</t>
+  </si>
+  <si>
+    <t>Sprint 9 Semana 9</t>
+  </si>
+  <si>
+    <t>Sprint 10 Semana 10</t>
+  </si>
+  <si>
+    <t>Sprint 11 Semanas 11 - 12</t>
+  </si>
+  <si>
+    <t>Sprint 12 Semanas 13 - 14</t>
+  </si>
+  <si>
+    <t>Sprint 13 Semanas 15 - 16</t>
+  </si>
+  <si>
+    <t>Sprint 14 Semanas 17 - 18</t>
   </si>
 </sst>
 </file>
@@ -6924,7 +6984,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -6983,6 +7043,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -77287,15 +77351,6 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:J424"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -90455,4 +90510,238 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:D20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="42.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>2057</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="19" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45940</v>
+      </c>
+      <c r="D2" s="29">
+        <v>45970</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="19" t="s">
+        <v>2058</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45962</v>
+      </c>
+      <c r="D3" s="29">
+        <v>45965</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="19" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45961</v>
+      </c>
+      <c r="D4" s="29">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="19" t="s">
+        <v>2059</v>
+      </c>
+      <c r="C5" s="28">
+        <v>46008</v>
+      </c>
+      <c r="D5" s="29">
+        <v>46013</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="19" t="s">
+        <v>2060</v>
+      </c>
+      <c r="C6" s="28">
+        <v>46008</v>
+      </c>
+      <c r="D6" s="29">
+        <v>46013</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="19" t="s">
+        <v>2062</v>
+      </c>
+      <c r="C7" s="28">
+        <v>46013</v>
+      </c>
+      <c r="D7" s="29">
+        <v>46020</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="19" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C8" s="28">
+        <v>46020</v>
+      </c>
+      <c r="D8" s="29">
+        <v>46027</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="19" t="s">
+        <v>2064</v>
+      </c>
+      <c r="C9" s="28">
+        <v>46027</v>
+      </c>
+      <c r="D9" s="29">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="19" t="s">
+        <v>2065</v>
+      </c>
+      <c r="C10" s="28">
+        <v>46034</v>
+      </c>
+      <c r="D10" s="29">
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="19" t="s">
+        <v>2066</v>
+      </c>
+      <c r="C11" s="28">
+        <v>46041</v>
+      </c>
+      <c r="D11" s="29">
+        <v>46048</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="19" t="s">
+        <v>2067</v>
+      </c>
+      <c r="C12" s="28">
+        <v>46048</v>
+      </c>
+      <c r="D12" s="29">
+        <v>46055</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="19" t="s">
+        <v>2068</v>
+      </c>
+      <c r="C13" s="28">
+        <v>46055</v>
+      </c>
+      <c r="D13" s="29">
+        <v>46062</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="19" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C14" s="28">
+        <v>46062</v>
+      </c>
+      <c r="D14" s="29">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="19" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C15" s="28">
+        <v>46069</v>
+      </c>
+      <c r="D15" s="29">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="19" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C16" s="28">
+        <v>46076</v>
+      </c>
+      <c r="D16" s="29">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="19" t="s">
+        <v>2072</v>
+      </c>
+      <c r="C17" s="28">
+        <v>46083</v>
+      </c>
+      <c r="D17" s="29">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="19" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C18" s="28">
+        <v>46097</v>
+      </c>
+      <c r="D18" s="29">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="19" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C19" s="28">
+        <v>46111</v>
+      </c>
+      <c r="D19" s="29">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="19" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C20" s="28">
+        <v>46125</v>
+      </c>
+      <c r="D20" s="29">
+        <v>46139</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Proyecto Intermodular/Jira/Tablas Jira.xlsx
+++ b/Proyecto Intermodular/Jira/Tablas Jira.xlsx
@@ -348,7 +348,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20760" uniqueCount="2076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20762" uniqueCount="2078">
   <si>
     <t>Resumen</t>
   </si>
@@ -6848,6 +6848,12 @@
   </si>
   <si>
     <t>Sprint 14 Semanas 17 - 18</t>
+  </si>
+  <si>
+    <t>Implementación y Pruebas</t>
+  </si>
+  <si>
+    <t>Documento de instalación, documento de manual de usuario y documento de cierre</t>
   </si>
 </sst>
 </file>
@@ -90514,7 +90520,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:D20"/>
+  <dimension ref="B1:D22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.7109375" customWidth="1"/>
@@ -90740,6 +90746,28 @@
         <v>46139</v>
       </c>
     </row>
+    <row r="21" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="19" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C21" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D21" s="29">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="19" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C22" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D22" s="29">
+        <v>46112</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
